--- a/assets/data/world-bank/excel/ove_banco_mundial_venezuela_infraestructura_y_digitalizacion.xlsx
+++ b/assets/data/world-bank/excel/ove_banco_mundial_venezuela_infraestructura_y_digitalizacion.xlsx
@@ -715,7 +715,7 @@
       </c>
       <c r="P7" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q7" s="4" t="n"/>
@@ -792,7 +792,7 @@
       </c>
       <c r="P8" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q8" s="4" t="n"/>
@@ -869,7 +869,7 @@
       </c>
       <c r="P9" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q9" s="4" t="n"/>
@@ -946,7 +946,7 @@
       </c>
       <c r="P10" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q10" s="4" t="n"/>
@@ -1023,7 +1023,7 @@
       </c>
       <c r="P11" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q11" s="4" t="n"/>
@@ -1100,7 +1100,7 @@
       </c>
       <c r="P12" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q12" s="4" t="n"/>
@@ -1177,7 +1177,7 @@
       </c>
       <c r="P13" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q13" s="4" t="n"/>
@@ -1254,7 +1254,7 @@
       </c>
       <c r="P14" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q14" s="4" t="n"/>
@@ -1331,7 +1331,7 @@
       </c>
       <c r="P15" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q15" s="4" t="n"/>
@@ -1408,7 +1408,7 @@
       </c>
       <c r="P16" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q16" s="4" t="n"/>
@@ -1487,7 +1487,7 @@
       </c>
       <c r="P17" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q17" s="4" t="n"/>
@@ -1566,7 +1566,7 @@
       </c>
       <c r="P18" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q18" s="4" t="n"/>
@@ -1645,7 +1645,7 @@
       </c>
       <c r="P19" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q19" s="4" t="n"/>
@@ -1724,7 +1724,7 @@
       </c>
       <c r="P20" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q20" s="4" t="n"/>
@@ -1803,7 +1803,7 @@
       </c>
       <c r="P21" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q21" s="4" t="n"/>
@@ -1882,7 +1882,7 @@
       </c>
       <c r="P22" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q22" s="4" t="n"/>
@@ -1961,7 +1961,7 @@
       </c>
       <c r="P23" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q23" s="4" t="n"/>
@@ -2040,7 +2040,7 @@
       </c>
       <c r="P24" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q24" s="4" t="n"/>
@@ -2119,7 +2119,7 @@
       </c>
       <c r="P25" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q25" s="4" t="n"/>
@@ -2198,7 +2198,7 @@
       </c>
       <c r="P26" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q26" s="4" t="n"/>
@@ -2277,7 +2277,7 @@
       </c>
       <c r="P27" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q27" s="4" t="n"/>
@@ -2356,7 +2356,7 @@
       </c>
       <c r="P28" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q28" s="4" t="n"/>
@@ -2435,7 +2435,7 @@
       </c>
       <c r="P29" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q29" s="4" t="n"/>
@@ -2514,7 +2514,7 @@
       </c>
       <c r="P30" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q30" s="4" t="n"/>
@@ -2593,7 +2593,7 @@
       </c>
       <c r="P31" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q31" s="4" t="n"/>
@@ -2672,7 +2672,7 @@
       </c>
       <c r="P32" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q32" s="4" t="n"/>
@@ -2751,7 +2751,7 @@
       </c>
       <c r="P33" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q33" s="4" t="n"/>
@@ -2830,7 +2830,7 @@
       </c>
       <c r="P34" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q34" s="4" t="n"/>
@@ -2909,7 +2909,7 @@
       </c>
       <c r="P35" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q35" s="4" t="n"/>
@@ -2988,7 +2988,7 @@
       </c>
       <c r="P36" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q36" s="4" t="n"/>
@@ -3067,7 +3067,7 @@
       </c>
       <c r="P37" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q37" s="4" t="n"/>
@@ -3146,7 +3146,7 @@
       </c>
       <c r="P38" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q38" s="4" t="n"/>
@@ -3225,7 +3225,7 @@
       </c>
       <c r="P39" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q39" s="4" t="n"/>
@@ -3304,7 +3304,7 @@
       </c>
       <c r="P40" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q40" s="4" t="n"/>
@@ -3383,7 +3383,7 @@
       </c>
       <c r="P41" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q41" s="4" t="n"/>
@@ -3462,7 +3462,7 @@
       </c>
       <c r="P42" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q42" s="4" t="n"/>
@@ -3541,7 +3541,7 @@
       </c>
       <c r="P43" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q43" s="4" t="n"/>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="P44" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q44" s="4" t="n"/>
@@ -3699,7 +3699,7 @@
       </c>
       <c r="P45" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q45" s="4" t="n"/>
@@ -3778,7 +3778,7 @@
       </c>
       <c r="P46" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q46" s="4" t="n"/>
@@ -3857,7 +3857,7 @@
       </c>
       <c r="P47" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q47" s="4" t="n"/>
@@ -3936,7 +3936,7 @@
       </c>
       <c r="P48" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q48" s="4" t="n"/>
@@ -4015,7 +4015,7 @@
       </c>
       <c r="P49" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q49" s="4" t="n"/>
@@ -4094,7 +4094,7 @@
       </c>
       <c r="P50" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q50" s="4" t="n"/>
@@ -4173,7 +4173,7 @@
       </c>
       <c r="P51" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q51" s="4" t="n"/>
@@ -4252,7 +4252,7 @@
       </c>
       <c r="P52" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q52" s="4" t="n"/>
@@ -4331,7 +4331,7 @@
       </c>
       <c r="P53" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q53" s="4" t="n"/>
@@ -4410,7 +4410,7 @@
       </c>
       <c r="P54" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q54" s="4" t="n"/>
@@ -4489,7 +4489,7 @@
       </c>
       <c r="P55" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q55" s="4" t="n"/>
@@ -4568,7 +4568,7 @@
       </c>
       <c r="P56" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q56" s="4" t="n"/>
@@ -4647,7 +4647,7 @@
       </c>
       <c r="P57" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q57" s="4" t="n"/>
@@ -4726,7 +4726,7 @@
       </c>
       <c r="P58" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q58" s="4" t="n"/>
@@ -4805,7 +4805,7 @@
       </c>
       <c r="P59" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q59" s="4" t="n"/>
@@ -4884,7 +4884,7 @@
       </c>
       <c r="P60" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q60" s="4" t="n"/>
@@ -4963,7 +4963,7 @@
       </c>
       <c r="P61" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q61" s="4" t="n"/>
@@ -5042,7 +5042,7 @@
       </c>
       <c r="P62" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q62" s="4" t="n"/>
@@ -5121,7 +5121,7 @@
       </c>
       <c r="P63" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q63" s="4" t="n"/>
@@ -5200,7 +5200,7 @@
       </c>
       <c r="P64" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q64" s="4" t="n"/>
@@ -5279,7 +5279,7 @@
       </c>
       <c r="P65" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q65" s="4" t="n"/>
@@ -5358,7 +5358,7 @@
       </c>
       <c r="P66" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q66" s="4" t="n"/>
@@ -5437,7 +5437,7 @@
       </c>
       <c r="P67" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q67" s="4" t="n"/>
@@ -5516,7 +5516,7 @@
       </c>
       <c r="P68" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q68" s="4" t="n"/>
@@ -5595,7 +5595,7 @@
       </c>
       <c r="P69" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q69" s="4" t="n"/>
@@ -5674,7 +5674,7 @@
       </c>
       <c r="P70" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q70" s="4" t="n"/>
@@ -5751,7 +5751,7 @@
       </c>
       <c r="P71" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q71" s="4" t="n"/>
@@ -5828,7 +5828,7 @@
       </c>
       <c r="P72" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q72" s="4" t="n"/>
@@ -5907,7 +5907,7 @@
       </c>
       <c r="P73" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q73" s="4" t="n"/>
@@ -5984,7 +5984,7 @@
       </c>
       <c r="P74" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q74" s="4" t="n"/>
@@ -6061,7 +6061,7 @@
       </c>
       <c r="P75" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q75" s="4" t="n"/>
@@ -6138,7 +6138,7 @@
       </c>
       <c r="P76" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q76" s="4" t="n"/>
@@ -6215,7 +6215,7 @@
       </c>
       <c r="P77" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q77" s="4" t="n"/>
@@ -6294,7 +6294,7 @@
       </c>
       <c r="P78" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q78" s="4" t="n"/>
@@ -6371,7 +6371,7 @@
       </c>
       <c r="P79" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q79" s="4" t="n"/>
@@ -6448,7 +6448,7 @@
       </c>
       <c r="P80" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q80" s="4" t="n"/>
@@ -6525,7 +6525,7 @@
       </c>
       <c r="P81" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q81" s="4" t="n"/>
@@ -6602,7 +6602,7 @@
       </c>
       <c r="P82" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q82" s="4" t="n"/>
@@ -6681,7 +6681,7 @@
       </c>
       <c r="P83" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q83" s="4" t="n"/>
@@ -6758,7 +6758,7 @@
       </c>
       <c r="P84" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q84" s="4" t="n"/>
@@ -6835,7 +6835,7 @@
       </c>
       <c r="P85" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q85" s="4" t="n"/>
@@ -6912,7 +6912,7 @@
       </c>
       <c r="P86" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q86" s="4" t="n"/>
@@ -6989,7 +6989,7 @@
       </c>
       <c r="P87" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q87" s="4" t="n"/>
@@ -7068,7 +7068,7 @@
       </c>
       <c r="P88" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q88" s="4" t="n"/>
@@ -7147,7 +7147,7 @@
       </c>
       <c r="P89" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q89" s="4" t="n"/>
@@ -7226,7 +7226,7 @@
       </c>
       <c r="P90" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q90" s="4" t="n"/>
@@ -7305,7 +7305,7 @@
       </c>
       <c r="P91" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q91" s="4" t="n"/>
@@ -7384,7 +7384,7 @@
       </c>
       <c r="P92" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q92" s="4" t="n"/>
@@ -7463,7 +7463,7 @@
       </c>
       <c r="P93" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q93" s="4" t="n"/>
@@ -7542,7 +7542,7 @@
       </c>
       <c r="P94" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q94" s="4" t="n"/>
@@ -7621,7 +7621,7 @@
       </c>
       <c r="P95" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q95" s="4" t="n"/>
@@ -7700,7 +7700,7 @@
       </c>
       <c r="P96" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q96" s="4" t="n"/>
@@ -7779,7 +7779,7 @@
       </c>
       <c r="P97" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q97" s="4" t="n"/>
@@ -7858,7 +7858,7 @@
       </c>
       <c r="P98" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q98" s="4" t="n"/>
@@ -7937,7 +7937,7 @@
       </c>
       <c r="P99" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q99" s="4" t="n"/>
@@ -8016,7 +8016,7 @@
       </c>
       <c r="P100" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q100" s="4" t="n"/>
@@ -8095,7 +8095,7 @@
       </c>
       <c r="P101" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q101" s="4" t="n"/>
@@ -8174,7 +8174,7 @@
       </c>
       <c r="P102" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q102" s="4" t="n"/>
@@ -8253,7 +8253,7 @@
       </c>
       <c r="P103" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q103" s="4" t="n"/>
@@ -8332,7 +8332,7 @@
       </c>
       <c r="P104" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q104" s="4" t="n"/>
@@ -8411,7 +8411,7 @@
       </c>
       <c r="P105" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q105" s="4" t="n"/>
@@ -8490,7 +8490,7 @@
       </c>
       <c r="P106" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q106" s="4" t="n"/>
@@ -8569,7 +8569,7 @@
       </c>
       <c r="P107" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q107" s="4" t="n"/>
@@ -8648,7 +8648,7 @@
       </c>
       <c r="P108" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q108" s="4" t="n"/>
@@ -8727,7 +8727,7 @@
       </c>
       <c r="P109" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q109" s="4" t="n"/>
@@ -8806,7 +8806,7 @@
       </c>
       <c r="P110" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q110" s="4" t="n"/>
@@ -8885,7 +8885,7 @@
       </c>
       <c r="P111" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q111" s="4" t="n"/>
@@ -8964,7 +8964,7 @@
       </c>
       <c r="P112" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q112" s="4" t="n"/>
@@ -9043,7 +9043,7 @@
       </c>
       <c r="P113" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q113" s="4" t="n"/>
@@ -9122,7 +9122,7 @@
       </c>
       <c r="P114" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q114" s="4" t="n"/>
@@ -9201,7 +9201,7 @@
       </c>
       <c r="P115" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q115" s="4" t="n"/>
@@ -9280,7 +9280,7 @@
       </c>
       <c r="P116" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q116" s="4" t="n"/>
@@ -9359,7 +9359,7 @@
       </c>
       <c r="P117" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q117" s="4" t="n"/>
@@ -9438,7 +9438,7 @@
       </c>
       <c r="P118" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q118" s="4" t="n"/>
@@ -9517,7 +9517,7 @@
       </c>
       <c r="P119" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q119" s="4" t="n"/>
@@ -9596,7 +9596,7 @@
       </c>
       <c r="P120" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q120" s="4" t="n"/>
@@ -9675,7 +9675,7 @@
       </c>
       <c r="P121" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q121" s="4" t="n"/>
@@ -9754,7 +9754,7 @@
       </c>
       <c r="P122" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q122" s="4" t="n"/>
@@ -9833,7 +9833,7 @@
       </c>
       <c r="P123" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q123" s="4" t="n"/>
@@ -9912,7 +9912,7 @@
       </c>
       <c r="P124" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q124" s="4" t="n"/>
@@ -9991,7 +9991,7 @@
       </c>
       <c r="P125" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q125" s="4" t="n"/>
@@ -10070,7 +10070,7 @@
       </c>
       <c r="P126" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q126" s="4" t="n"/>
@@ -10149,7 +10149,7 @@
       </c>
       <c r="P127" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q127" s="4" t="n"/>
@@ -10228,7 +10228,7 @@
       </c>
       <c r="P128" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q128" s="4" t="n"/>
@@ -10307,7 +10307,7 @@
       </c>
       <c r="P129" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q129" s="4" t="n"/>
@@ -10386,7 +10386,7 @@
       </c>
       <c r="P130" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q130" s="4" t="n"/>
@@ -10465,7 +10465,7 @@
       </c>
       <c r="P131" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q131" s="4" t="n"/>
@@ -10544,7 +10544,7 @@
       </c>
       <c r="P132" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q132" s="4" t="n"/>
@@ -10623,7 +10623,7 @@
       </c>
       <c r="P133" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q133" s="4" t="n"/>
@@ -10702,7 +10702,7 @@
       </c>
       <c r="P134" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q134" s="4" t="n"/>
@@ -10781,7 +10781,7 @@
       </c>
       <c r="P135" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q135" s="4" t="n"/>
@@ -10860,7 +10860,7 @@
       </c>
       <c r="P136" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q136" s="4" t="n"/>
@@ -10939,7 +10939,7 @@
       </c>
       <c r="P137" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q137" s="4" t="n"/>
@@ -11016,7 +11016,7 @@
       </c>
       <c r="P138" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q138" s="4" t="n"/>
@@ -11093,7 +11093,7 @@
       </c>
       <c r="P139" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q139" s="4" t="n"/>
@@ -11170,7 +11170,7 @@
       </c>
       <c r="P140" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q140" s="4" t="n"/>
@@ -11247,7 +11247,7 @@
       </c>
       <c r="P141" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q141" s="4" t="n"/>
@@ -11324,7 +11324,7 @@
       </c>
       <c r="P142" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q142" s="4" t="n"/>
@@ -11401,7 +11401,7 @@
       </c>
       <c r="P143" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q143" s="4" t="n"/>
@@ -11478,7 +11478,7 @@
       </c>
       <c r="P144" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q144" s="4" t="n"/>
@@ -11555,7 +11555,7 @@
       </c>
       <c r="P145" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q145" s="4" t="n"/>
@@ -11632,7 +11632,7 @@
       </c>
       <c r="P146" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q146" s="4" t="n"/>
@@ -11709,7 +11709,7 @@
       </c>
       <c r="P147" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q147" s="4" t="n"/>
@@ -11786,7 +11786,7 @@
       </c>
       <c r="P148" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q148" s="4" t="n"/>
@@ -11863,7 +11863,7 @@
       </c>
       <c r="P149" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q149" s="4" t="n"/>
@@ -11940,7 +11940,7 @@
       </c>
       <c r="P150" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q150" s="4" t="n"/>
@@ -12017,7 +12017,7 @@
       </c>
       <c r="P151" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q151" s="4" t="n"/>
@@ -12094,7 +12094,7 @@
       </c>
       <c r="P152" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q152" s="4" t="n"/>
@@ -12171,7 +12171,7 @@
       </c>
       <c r="P153" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q153" s="4" t="n"/>
@@ -12248,7 +12248,7 @@
       </c>
       <c r="P154" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q154" s="4" t="n"/>
@@ -12325,7 +12325,7 @@
       </c>
       <c r="P155" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q155" s="4" t="n"/>
@@ -12402,7 +12402,7 @@
       </c>
       <c r="P156" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q156" s="4" t="n"/>
@@ -12479,7 +12479,7 @@
       </c>
       <c r="P157" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q157" s="4" t="n"/>
@@ -12556,7 +12556,7 @@
       </c>
       <c r="P158" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q158" s="4" t="n"/>
@@ -12633,7 +12633,7 @@
       </c>
       <c r="P159" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q159" s="4" t="n"/>
@@ -12710,7 +12710,7 @@
       </c>
       <c r="P160" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q160" s="4" t="n"/>
@@ -12787,7 +12787,7 @@
       </c>
       <c r="P161" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q161" s="4" t="n"/>
@@ -12864,7 +12864,7 @@
       </c>
       <c r="P162" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q162" s="4" t="n"/>
@@ -12941,7 +12941,7 @@
       </c>
       <c r="P163" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q163" s="4" t="n"/>
@@ -13018,7 +13018,7 @@
       </c>
       <c r="P164" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q164" s="4" t="n"/>
@@ -13095,7 +13095,7 @@
       </c>
       <c r="P165" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q165" s="4" t="n"/>
@@ -13172,7 +13172,7 @@
       </c>
       <c r="P166" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q166" s="4" t="n"/>
@@ -13249,7 +13249,7 @@
       </c>
       <c r="P167" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q167" s="4" t="n"/>
@@ -13326,7 +13326,7 @@
       </c>
       <c r="P168" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q168" s="4" t="n"/>
@@ -13403,7 +13403,7 @@
       </c>
       <c r="P169" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q169" s="4" t="n"/>
@@ -13480,7 +13480,7 @@
       </c>
       <c r="P170" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q170" s="4" t="n"/>
@@ -13557,7 +13557,7 @@
       </c>
       <c r="P171" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q171" s="4" t="n"/>
@@ -13634,7 +13634,7 @@
       </c>
       <c r="P172" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q172" s="4" t="n"/>
@@ -13711,7 +13711,7 @@
       </c>
       <c r="P173" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q173" s="4" t="n"/>
@@ -13788,7 +13788,7 @@
       </c>
       <c r="P174" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q174" s="4" t="n"/>
@@ -13865,7 +13865,7 @@
       </c>
       <c r="P175" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q175" s="4" t="n"/>
@@ -13942,7 +13942,7 @@
       </c>
       <c r="P176" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q176" s="4" t="n"/>
@@ -14019,7 +14019,7 @@
       </c>
       <c r="P177" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q177" s="4" t="n"/>
@@ -14096,7 +14096,7 @@
       </c>
       <c r="P178" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q178" s="4" t="n"/>
@@ -14175,7 +14175,7 @@
       </c>
       <c r="P179" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q179" s="4" t="n"/>
@@ -14254,7 +14254,7 @@
       </c>
       <c r="P180" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q180" s="4" t="n"/>
@@ -14333,7 +14333,7 @@
       </c>
       <c r="P181" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q181" s="4" t="n"/>
@@ -14412,7 +14412,7 @@
       </c>
       <c r="P182" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q182" s="4" t="n"/>
@@ -14491,7 +14491,7 @@
       </c>
       <c r="P183" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q183" s="4" t="n"/>
@@ -14570,7 +14570,7 @@
       </c>
       <c r="P184" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q184" s="4" t="n"/>
@@ -14649,7 +14649,7 @@
       </c>
       <c r="P185" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q185" s="4" t="n"/>
@@ -14728,7 +14728,7 @@
       </c>
       <c r="P186" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q186" s="4" t="n"/>
@@ -14807,7 +14807,7 @@
       </c>
       <c r="P187" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q187" s="4" t="n"/>
@@ -14886,7 +14886,7 @@
       </c>
       <c r="P188" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q188" s="4" t="n"/>
@@ -14965,7 +14965,7 @@
       </c>
       <c r="P189" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q189" s="4" t="n"/>
@@ -15044,7 +15044,7 @@
       </c>
       <c r="P190" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q190" s="4" t="n"/>
@@ -15123,7 +15123,7 @@
       </c>
       <c r="P191" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q191" s="4" t="n"/>
@@ -15202,7 +15202,7 @@
       </c>
       <c r="P192" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q192" s="4" t="n"/>
@@ -15281,7 +15281,7 @@
       </c>
       <c r="P193" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q193" s="4" t="n"/>
@@ -15360,7 +15360,7 @@
       </c>
       <c r="P194" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q194" s="4" t="n"/>
@@ -15439,7 +15439,7 @@
       </c>
       <c r="P195" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q195" s="4" t="n"/>
@@ -15518,7 +15518,7 @@
       </c>
       <c r="P196" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q196" s="4" t="n"/>
@@ -15597,7 +15597,7 @@
       </c>
       <c r="P197" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q197" s="4" t="n"/>
@@ -15676,7 +15676,7 @@
       </c>
       <c r="P198" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q198" s="4" t="n"/>
@@ -15755,7 +15755,7 @@
       </c>
       <c r="P199" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q199" s="4" t="n"/>
@@ -15834,7 +15834,7 @@
       </c>
       <c r="P200" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q200" s="4" t="n"/>
@@ -15913,7 +15913,7 @@
       </c>
       <c r="P201" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q201" s="4" t="n"/>
@@ -15992,7 +15992,7 @@
       </c>
       <c r="P202" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q202" s="4" t="n"/>
@@ -16071,7 +16071,7 @@
       </c>
       <c r="P203" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q203" s="4" t="n"/>
@@ -16148,7 +16148,7 @@
       </c>
       <c r="P204" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q204" s="4" t="n"/>
@@ -16225,7 +16225,7 @@
       </c>
       <c r="P205" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q205" s="4" t="n"/>
@@ -16302,7 +16302,7 @@
       </c>
       <c r="P206" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q206" s="4" t="n"/>
@@ -16379,7 +16379,7 @@
       </c>
       <c r="P207" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q207" s="4" t="n"/>
@@ -16456,7 +16456,7 @@
       </c>
       <c r="P208" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q208" s="4" t="n"/>
@@ -16533,7 +16533,7 @@
       </c>
       <c r="P209" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q209" s="4" t="n"/>
@@ -16610,7 +16610,7 @@
       </c>
       <c r="P210" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q210" s="4" t="n"/>
@@ -16687,7 +16687,7 @@
       </c>
       <c r="P211" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q211" s="4" t="n"/>
@@ -16764,7 +16764,7 @@
       </c>
       <c r="P212" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q212" s="4" t="n"/>
@@ -16841,7 +16841,7 @@
       </c>
       <c r="P213" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q213" s="4" t="n"/>
@@ -16918,7 +16918,7 @@
       </c>
       <c r="P214" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q214" s="4" t="n"/>
@@ -16995,7 +16995,7 @@
       </c>
       <c r="P215" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q215" s="4" t="n"/>
@@ -17072,7 +17072,7 @@
       </c>
       <c r="P216" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q216" s="4" t="n"/>
@@ -17149,7 +17149,7 @@
       </c>
       <c r="P217" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q217" s="4" t="n"/>
@@ -17226,7 +17226,7 @@
       </c>
       <c r="P218" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q218" s="4" t="n"/>
@@ -17303,7 +17303,7 @@
       </c>
       <c r="P219" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q219" s="4" t="n"/>
@@ -17380,7 +17380,7 @@
       </c>
       <c r="P220" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q220" s="4" t="n"/>
@@ -17457,7 +17457,7 @@
       </c>
       <c r="P221" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q221" s="4" t="n"/>
@@ -17534,7 +17534,7 @@
       </c>
       <c r="P222" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q222" s="4" t="n"/>
@@ -17611,7 +17611,7 @@
       </c>
       <c r="P223" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q223" s="4" t="n"/>
@@ -17688,7 +17688,7 @@
       </c>
       <c r="P224" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q224" s="4" t="n"/>
@@ -17765,7 +17765,7 @@
       </c>
       <c r="P225" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q225" s="4" t="n"/>
@@ -17842,7 +17842,7 @@
       </c>
       <c r="P226" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q226" s="4" t="n"/>
@@ -17919,7 +17919,7 @@
       </c>
       <c r="P227" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q227" s="4" t="n"/>
@@ -17996,7 +17996,7 @@
       </c>
       <c r="P228" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q228" s="4" t="n"/>
@@ -18073,7 +18073,7 @@
       </c>
       <c r="P229" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q229" s="4" t="n"/>
@@ -18150,7 +18150,7 @@
       </c>
       <c r="P230" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q230" s="4" t="n"/>
@@ -18227,7 +18227,7 @@
       </c>
       <c r="P231" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q231" s="4" t="n"/>
@@ -18304,7 +18304,7 @@
       </c>
       <c r="P232" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q232" s="4" t="n"/>
@@ -18381,7 +18381,7 @@
       </c>
       <c r="P233" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q233" s="4" t="n"/>
@@ -18458,7 +18458,7 @@
       </c>
       <c r="P234" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q234" s="4" t="n"/>
@@ -18537,7 +18537,7 @@
       </c>
       <c r="P235" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q235" s="4" t="n"/>
@@ -18614,7 +18614,7 @@
       </c>
       <c r="P236" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q236" s="4" t="n"/>
@@ -18693,7 +18693,7 @@
       </c>
       <c r="P237" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q237" s="4" t="n"/>
@@ -18772,7 +18772,7 @@
       </c>
       <c r="P238" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q238" s="4" t="n"/>
@@ -18851,7 +18851,7 @@
       </c>
       <c r="P239" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q239" s="4" t="n"/>
@@ -18930,7 +18930,7 @@
       </c>
       <c r="P240" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q240" s="4" t="n"/>
@@ -19009,7 +19009,7 @@
       </c>
       <c r="P241" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q241" s="4" t="n"/>
@@ -19088,7 +19088,7 @@
       </c>
       <c r="P242" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q242" s="4" t="n"/>
@@ -19167,7 +19167,7 @@
       </c>
       <c r="P243" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q243" s="4" t="n"/>
@@ -19246,7 +19246,7 @@
       </c>
       <c r="P244" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q244" s="4" t="n"/>
@@ -19325,7 +19325,7 @@
       </c>
       <c r="P245" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q245" s="4" t="n"/>
@@ -19404,7 +19404,7 @@
       </c>
       <c r="P246" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q246" s="4" t="n"/>
@@ -19483,7 +19483,7 @@
       </c>
       <c r="P247" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q247" s="4" t="n"/>
@@ -19562,7 +19562,7 @@
       </c>
       <c r="P248" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q248" s="4" t="n"/>
@@ -19641,7 +19641,7 @@
       </c>
       <c r="P249" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q249" s="4" t="n"/>
@@ -19720,7 +19720,7 @@
       </c>
       <c r="P250" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q250" s="4" t="n"/>
@@ -19799,7 +19799,7 @@
       </c>
       <c r="P251" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q251" s="4" t="n"/>
@@ -19878,7 +19878,7 @@
       </c>
       <c r="P252" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q252" s="4" t="n"/>
@@ -19957,7 +19957,7 @@
       </c>
       <c r="P253" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q253" s="4" t="n"/>
@@ -20036,7 +20036,7 @@
       </c>
       <c r="P254" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q254" s="4" t="n"/>
@@ -20115,7 +20115,7 @@
       </c>
       <c r="P255" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q255" s="4" t="n"/>
@@ -20194,7 +20194,7 @@
       </c>
       <c r="P256" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q256" s="4" t="n"/>
@@ -20273,7 +20273,7 @@
       </c>
       <c r="P257" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q257" s="4" t="n"/>
@@ -20352,7 +20352,7 @@
       </c>
       <c r="P258" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q258" s="4" t="n"/>
@@ -20431,7 +20431,7 @@
       </c>
       <c r="P259" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q259" s="4" t="n"/>
@@ -20510,7 +20510,7 @@
       </c>
       <c r="P260" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q260" s="4" t="n"/>
@@ -20589,7 +20589,7 @@
       </c>
       <c r="P261" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q261" s="4" t="n"/>
@@ -20666,7 +20666,7 @@
       </c>
       <c r="P262" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q262" s="4" t="n"/>
@@ -20743,7 +20743,7 @@
       </c>
       <c r="P263" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q263" s="4" t="n"/>
@@ -20822,7 +20822,7 @@
       </c>
       <c r="P264" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q264" s="4" t="n"/>
@@ -20901,7 +20901,7 @@
       </c>
       <c r="P265" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q265" s="4" t="n"/>
@@ -20980,7 +20980,7 @@
       </c>
       <c r="P266" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q266" s="4" t="n"/>
@@ -21059,7 +21059,7 @@
       </c>
       <c r="P267" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q267" s="4" t="n"/>
@@ -21138,7 +21138,7 @@
       </c>
       <c r="P268" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q268" s="4" t="n"/>
@@ -21217,7 +21217,7 @@
       </c>
       <c r="P269" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q269" s="4" t="n"/>
@@ -21294,7 +21294,7 @@
       </c>
       <c r="P270" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q270" s="4" t="n"/>
@@ -21379,7 +21379,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
     </row>

--- a/assets/data/world-bank/excel/ove_banco_mundial_venezuela_infraestructura_y_digitalizacion.xlsx
+++ b/assets/data/world-bank/excel/ove_banco_mundial_venezuela_infraestructura_y_digitalizacion.xlsx
@@ -715,7 +715,7 @@
       </c>
       <c r="P7" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q7" s="4" t="n"/>
@@ -792,7 +792,7 @@
       </c>
       <c r="P8" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q8" s="4" t="n"/>
@@ -869,7 +869,7 @@
       </c>
       <c r="P9" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q9" s="4" t="n"/>
@@ -946,7 +946,7 @@
       </c>
       <c r="P10" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q10" s="4" t="n"/>
@@ -1023,7 +1023,7 @@
       </c>
       <c r="P11" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q11" s="4" t="n"/>
@@ -1100,7 +1100,7 @@
       </c>
       <c r="P12" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q12" s="4" t="n"/>
@@ -1177,7 +1177,7 @@
       </c>
       <c r="P13" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q13" s="4" t="n"/>
@@ -1254,7 +1254,7 @@
       </c>
       <c r="P14" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q14" s="4" t="n"/>
@@ -1331,7 +1331,7 @@
       </c>
       <c r="P15" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q15" s="4" t="n"/>
@@ -1408,7 +1408,7 @@
       </c>
       <c r="P16" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q16" s="4" t="n"/>
@@ -1487,7 +1487,7 @@
       </c>
       <c r="P17" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q17" s="4" t="n"/>
@@ -1566,7 +1566,7 @@
       </c>
       <c r="P18" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q18" s="4" t="n"/>
@@ -1645,7 +1645,7 @@
       </c>
       <c r="P19" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q19" s="4" t="n"/>
@@ -1724,7 +1724,7 @@
       </c>
       <c r="P20" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q20" s="4" t="n"/>
@@ -1803,7 +1803,7 @@
       </c>
       <c r="P21" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q21" s="4" t="n"/>
@@ -1882,7 +1882,7 @@
       </c>
       <c r="P22" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q22" s="4" t="n"/>
@@ -1961,7 +1961,7 @@
       </c>
       <c r="P23" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q23" s="4" t="n"/>
@@ -2040,7 +2040,7 @@
       </c>
       <c r="P24" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q24" s="4" t="n"/>
@@ -2119,7 +2119,7 @@
       </c>
       <c r="P25" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q25" s="4" t="n"/>
@@ -2198,7 +2198,7 @@
       </c>
       <c r="P26" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q26" s="4" t="n"/>
@@ -2277,7 +2277,7 @@
       </c>
       <c r="P27" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q27" s="4" t="n"/>
@@ -2356,7 +2356,7 @@
       </c>
       <c r="P28" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q28" s="4" t="n"/>
@@ -2435,7 +2435,7 @@
       </c>
       <c r="P29" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q29" s="4" t="n"/>
@@ -2514,7 +2514,7 @@
       </c>
       <c r="P30" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q30" s="4" t="n"/>
@@ -2593,7 +2593,7 @@
       </c>
       <c r="P31" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q31" s="4" t="n"/>
@@ -2672,7 +2672,7 @@
       </c>
       <c r="P32" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q32" s="4" t="n"/>
@@ -2751,7 +2751,7 @@
       </c>
       <c r="P33" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q33" s="4" t="n"/>
@@ -2830,7 +2830,7 @@
       </c>
       <c r="P34" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q34" s="4" t="n"/>
@@ -2909,7 +2909,7 @@
       </c>
       <c r="P35" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q35" s="4" t="n"/>
@@ -2988,7 +2988,7 @@
       </c>
       <c r="P36" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q36" s="4" t="n"/>
@@ -3067,7 +3067,7 @@
       </c>
       <c r="P37" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q37" s="4" t="n"/>
@@ -3146,7 +3146,7 @@
       </c>
       <c r="P38" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q38" s="4" t="n"/>
@@ -3225,7 +3225,7 @@
       </c>
       <c r="P39" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q39" s="4" t="n"/>
@@ -3304,7 +3304,7 @@
       </c>
       <c r="P40" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q40" s="4" t="n"/>
@@ -3383,7 +3383,7 @@
       </c>
       <c r="P41" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q41" s="4" t="n"/>
@@ -3462,7 +3462,7 @@
       </c>
       <c r="P42" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q42" s="4" t="n"/>
@@ -3541,7 +3541,7 @@
       </c>
       <c r="P43" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q43" s="4" t="n"/>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="P44" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q44" s="4" t="n"/>
@@ -3699,7 +3699,7 @@
       </c>
       <c r="P45" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q45" s="4" t="n"/>
@@ -3778,7 +3778,7 @@
       </c>
       <c r="P46" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q46" s="4" t="n"/>
@@ -3857,7 +3857,7 @@
       </c>
       <c r="P47" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q47" s="4" t="n"/>
@@ -3936,7 +3936,7 @@
       </c>
       <c r="P48" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q48" s="4" t="n"/>
@@ -4015,7 +4015,7 @@
       </c>
       <c r="P49" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q49" s="4" t="n"/>
@@ -4094,7 +4094,7 @@
       </c>
       <c r="P50" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q50" s="4" t="n"/>
@@ -4173,7 +4173,7 @@
       </c>
       <c r="P51" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q51" s="4" t="n"/>
@@ -4252,7 +4252,7 @@
       </c>
       <c r="P52" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q52" s="4" t="n"/>
@@ -4331,7 +4331,7 @@
       </c>
       <c r="P53" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q53" s="4" t="n"/>
@@ -4410,7 +4410,7 @@
       </c>
       <c r="P54" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q54" s="4" t="n"/>
@@ -4489,7 +4489,7 @@
       </c>
       <c r="P55" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q55" s="4" t="n"/>
@@ -4568,7 +4568,7 @@
       </c>
       <c r="P56" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q56" s="4" t="n"/>
@@ -4647,7 +4647,7 @@
       </c>
       <c r="P57" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q57" s="4" t="n"/>
@@ -4726,7 +4726,7 @@
       </c>
       <c r="P58" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q58" s="4" t="n"/>
@@ -4805,7 +4805,7 @@
       </c>
       <c r="P59" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q59" s="4" t="n"/>
@@ -4884,7 +4884,7 @@
       </c>
       <c r="P60" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q60" s="4" t="n"/>
@@ -4963,7 +4963,7 @@
       </c>
       <c r="P61" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q61" s="4" t="n"/>
@@ -5042,7 +5042,7 @@
       </c>
       <c r="P62" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q62" s="4" t="n"/>
@@ -5121,7 +5121,7 @@
       </c>
       <c r="P63" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q63" s="4" t="n"/>
@@ -5200,7 +5200,7 @@
       </c>
       <c r="P64" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q64" s="4" t="n"/>
@@ -5279,7 +5279,7 @@
       </c>
       <c r="P65" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q65" s="4" t="n"/>
@@ -5358,7 +5358,7 @@
       </c>
       <c r="P66" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q66" s="4" t="n"/>
@@ -5437,7 +5437,7 @@
       </c>
       <c r="P67" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q67" s="4" t="n"/>
@@ -5516,7 +5516,7 @@
       </c>
       <c r="P68" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q68" s="4" t="n"/>
@@ -5595,7 +5595,7 @@
       </c>
       <c r="P69" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q69" s="4" t="n"/>
@@ -5674,7 +5674,7 @@
       </c>
       <c r="P70" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q70" s="4" t="n"/>
@@ -5751,7 +5751,7 @@
       </c>
       <c r="P71" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q71" s="4" t="n"/>
@@ -5828,7 +5828,7 @@
       </c>
       <c r="P72" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q72" s="4" t="n"/>
@@ -5907,7 +5907,7 @@
       </c>
       <c r="P73" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q73" s="4" t="n"/>
@@ -5984,7 +5984,7 @@
       </c>
       <c r="P74" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q74" s="4" t="n"/>
@@ -6061,7 +6061,7 @@
       </c>
       <c r="P75" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q75" s="4" t="n"/>
@@ -6138,7 +6138,7 @@
       </c>
       <c r="P76" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q76" s="4" t="n"/>
@@ -6215,7 +6215,7 @@
       </c>
       <c r="P77" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q77" s="4" t="n"/>
@@ -6294,7 +6294,7 @@
       </c>
       <c r="P78" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q78" s="4" t="n"/>
@@ -6371,7 +6371,7 @@
       </c>
       <c r="P79" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q79" s="4" t="n"/>
@@ -6448,7 +6448,7 @@
       </c>
       <c r="P80" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q80" s="4" t="n"/>
@@ -6525,7 +6525,7 @@
       </c>
       <c r="P81" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q81" s="4" t="n"/>
@@ -6602,7 +6602,7 @@
       </c>
       <c r="P82" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q82" s="4" t="n"/>
@@ -6681,7 +6681,7 @@
       </c>
       <c r="P83" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q83" s="4" t="n"/>
@@ -6758,7 +6758,7 @@
       </c>
       <c r="P84" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q84" s="4" t="n"/>
@@ -6835,7 +6835,7 @@
       </c>
       <c r="P85" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q85" s="4" t="n"/>
@@ -6912,7 +6912,7 @@
       </c>
       <c r="P86" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q86" s="4" t="n"/>
@@ -6989,7 +6989,7 @@
       </c>
       <c r="P87" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q87" s="4" t="n"/>
@@ -7068,7 +7068,7 @@
       </c>
       <c r="P88" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q88" s="4" t="n"/>
@@ -7147,7 +7147,7 @@
       </c>
       <c r="P89" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q89" s="4" t="n"/>
@@ -7226,7 +7226,7 @@
       </c>
       <c r="P90" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q90" s="4" t="n"/>
@@ -7305,7 +7305,7 @@
       </c>
       <c r="P91" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q91" s="4" t="n"/>
@@ -7384,7 +7384,7 @@
       </c>
       <c r="P92" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q92" s="4" t="n"/>
@@ -7463,7 +7463,7 @@
       </c>
       <c r="P93" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q93" s="4" t="n"/>
@@ -7542,7 +7542,7 @@
       </c>
       <c r="P94" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q94" s="4" t="n"/>
@@ -7621,7 +7621,7 @@
       </c>
       <c r="P95" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q95" s="4" t="n"/>
@@ -7700,7 +7700,7 @@
       </c>
       <c r="P96" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q96" s="4" t="n"/>
@@ -7779,7 +7779,7 @@
       </c>
       <c r="P97" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q97" s="4" t="n"/>
@@ -7858,7 +7858,7 @@
       </c>
       <c r="P98" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q98" s="4" t="n"/>
@@ -7937,7 +7937,7 @@
       </c>
       <c r="P99" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q99" s="4" t="n"/>
@@ -8016,7 +8016,7 @@
       </c>
       <c r="P100" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q100" s="4" t="n"/>
@@ -8095,7 +8095,7 @@
       </c>
       <c r="P101" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q101" s="4" t="n"/>
@@ -8174,7 +8174,7 @@
       </c>
       <c r="P102" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q102" s="4" t="n"/>
@@ -8253,7 +8253,7 @@
       </c>
       <c r="P103" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q103" s="4" t="n"/>
@@ -8332,7 +8332,7 @@
       </c>
       <c r="P104" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q104" s="4" t="n"/>
@@ -8411,7 +8411,7 @@
       </c>
       <c r="P105" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q105" s="4" t="n"/>
@@ -8490,7 +8490,7 @@
       </c>
       <c r="P106" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q106" s="4" t="n"/>
@@ -8569,7 +8569,7 @@
       </c>
       <c r="P107" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q107" s="4" t="n"/>
@@ -8648,7 +8648,7 @@
       </c>
       <c r="P108" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q108" s="4" t="n"/>
@@ -8727,7 +8727,7 @@
       </c>
       <c r="P109" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q109" s="4" t="n"/>
@@ -8806,7 +8806,7 @@
       </c>
       <c r="P110" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q110" s="4" t="n"/>
@@ -8885,7 +8885,7 @@
       </c>
       <c r="P111" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q111" s="4" t="n"/>
@@ -8964,7 +8964,7 @@
       </c>
       <c r="P112" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q112" s="4" t="n"/>
@@ -9043,7 +9043,7 @@
       </c>
       <c r="P113" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q113" s="4" t="n"/>
@@ -9122,7 +9122,7 @@
       </c>
       <c r="P114" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q114" s="4" t="n"/>
@@ -9201,7 +9201,7 @@
       </c>
       <c r="P115" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q115" s="4" t="n"/>
@@ -9280,7 +9280,7 @@
       </c>
       <c r="P116" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q116" s="4" t="n"/>
@@ -9359,7 +9359,7 @@
       </c>
       <c r="P117" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q117" s="4" t="n"/>
@@ -9438,7 +9438,7 @@
       </c>
       <c r="P118" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q118" s="4" t="n"/>
@@ -9517,7 +9517,7 @@
       </c>
       <c r="P119" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q119" s="4" t="n"/>
@@ -9596,7 +9596,7 @@
       </c>
       <c r="P120" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q120" s="4" t="n"/>
@@ -9675,7 +9675,7 @@
       </c>
       <c r="P121" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q121" s="4" t="n"/>
@@ -9754,7 +9754,7 @@
       </c>
       <c r="P122" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q122" s="4" t="n"/>
@@ -9833,7 +9833,7 @@
       </c>
       <c r="P123" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q123" s="4" t="n"/>
@@ -9912,7 +9912,7 @@
       </c>
       <c r="P124" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q124" s="4" t="n"/>
@@ -9991,7 +9991,7 @@
       </c>
       <c r="P125" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q125" s="4" t="n"/>
@@ -10070,7 +10070,7 @@
       </c>
       <c r="P126" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q126" s="4" t="n"/>
@@ -10149,7 +10149,7 @@
       </c>
       <c r="P127" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q127" s="4" t="n"/>
@@ -10228,7 +10228,7 @@
       </c>
       <c r="P128" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q128" s="4" t="n"/>
@@ -10307,7 +10307,7 @@
       </c>
       <c r="P129" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q129" s="4" t="n"/>
@@ -10386,7 +10386,7 @@
       </c>
       <c r="P130" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q130" s="4" t="n"/>
@@ -10465,7 +10465,7 @@
       </c>
       <c r="P131" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q131" s="4" t="n"/>
@@ -10544,7 +10544,7 @@
       </c>
       <c r="P132" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q132" s="4" t="n"/>
@@ -10623,7 +10623,7 @@
       </c>
       <c r="P133" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q133" s="4" t="n"/>
@@ -10702,7 +10702,7 @@
       </c>
       <c r="P134" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q134" s="4" t="n"/>
@@ -10781,7 +10781,7 @@
       </c>
       <c r="P135" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q135" s="4" t="n"/>
@@ -10860,7 +10860,7 @@
       </c>
       <c r="P136" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q136" s="4" t="n"/>
@@ -10939,7 +10939,7 @@
       </c>
       <c r="P137" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q137" s="4" t="n"/>
@@ -11016,7 +11016,7 @@
       </c>
       <c r="P138" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q138" s="4" t="n"/>
@@ -11093,7 +11093,7 @@
       </c>
       <c r="P139" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q139" s="4" t="n"/>
@@ -11170,7 +11170,7 @@
       </c>
       <c r="P140" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q140" s="4" t="n"/>
@@ -11247,7 +11247,7 @@
       </c>
       <c r="P141" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q141" s="4" t="n"/>
@@ -11324,7 +11324,7 @@
       </c>
       <c r="P142" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q142" s="4" t="n"/>
@@ -11401,7 +11401,7 @@
       </c>
       <c r="P143" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q143" s="4" t="n"/>
@@ -11478,7 +11478,7 @@
       </c>
       <c r="P144" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q144" s="4" t="n"/>
@@ -11555,7 +11555,7 @@
       </c>
       <c r="P145" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q145" s="4" t="n"/>
@@ -11632,7 +11632,7 @@
       </c>
       <c r="P146" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q146" s="4" t="n"/>
@@ -11709,7 +11709,7 @@
       </c>
       <c r="P147" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q147" s="4" t="n"/>
@@ -11786,7 +11786,7 @@
       </c>
       <c r="P148" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q148" s="4" t="n"/>
@@ -11863,7 +11863,7 @@
       </c>
       <c r="P149" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q149" s="4" t="n"/>
@@ -11940,7 +11940,7 @@
       </c>
       <c r="P150" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q150" s="4" t="n"/>
@@ -12017,7 +12017,7 @@
       </c>
       <c r="P151" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q151" s="4" t="n"/>
@@ -12094,7 +12094,7 @@
       </c>
       <c r="P152" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q152" s="4" t="n"/>
@@ -12171,7 +12171,7 @@
       </c>
       <c r="P153" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q153" s="4" t="n"/>
@@ -12248,7 +12248,7 @@
       </c>
       <c r="P154" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q154" s="4" t="n"/>
@@ -12325,7 +12325,7 @@
       </c>
       <c r="P155" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q155" s="4" t="n"/>
@@ -12402,7 +12402,7 @@
       </c>
       <c r="P156" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q156" s="4" t="n"/>
@@ -12479,7 +12479,7 @@
       </c>
       <c r="P157" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q157" s="4" t="n"/>
@@ -12556,7 +12556,7 @@
       </c>
       <c r="P158" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q158" s="4" t="n"/>
@@ -12633,7 +12633,7 @@
       </c>
       <c r="P159" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q159" s="4" t="n"/>
@@ -12710,7 +12710,7 @@
       </c>
       <c r="P160" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q160" s="4" t="n"/>
@@ -12787,7 +12787,7 @@
       </c>
       <c r="P161" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q161" s="4" t="n"/>
@@ -12864,7 +12864,7 @@
       </c>
       <c r="P162" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q162" s="4" t="n"/>
@@ -12941,7 +12941,7 @@
       </c>
       <c r="P163" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q163" s="4" t="n"/>
@@ -13018,7 +13018,7 @@
       </c>
       <c r="P164" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q164" s="4" t="n"/>
@@ -13095,7 +13095,7 @@
       </c>
       <c r="P165" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q165" s="4" t="n"/>
@@ -13172,7 +13172,7 @@
       </c>
       <c r="P166" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q166" s="4" t="n"/>
@@ -13249,7 +13249,7 @@
       </c>
       <c r="P167" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q167" s="4" t="n"/>
@@ -13326,7 +13326,7 @@
       </c>
       <c r="P168" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q168" s="4" t="n"/>
@@ -13403,7 +13403,7 @@
       </c>
       <c r="P169" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q169" s="4" t="n"/>
@@ -13480,7 +13480,7 @@
       </c>
       <c r="P170" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q170" s="4" t="n"/>
@@ -13557,7 +13557,7 @@
       </c>
       <c r="P171" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q171" s="4" t="n"/>
@@ -13634,7 +13634,7 @@
       </c>
       <c r="P172" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q172" s="4" t="n"/>
@@ -13711,7 +13711,7 @@
       </c>
       <c r="P173" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q173" s="4" t="n"/>
@@ -13788,7 +13788,7 @@
       </c>
       <c r="P174" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q174" s="4" t="n"/>
@@ -13865,7 +13865,7 @@
       </c>
       <c r="P175" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q175" s="4" t="n"/>
@@ -13942,7 +13942,7 @@
       </c>
       <c r="P176" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q176" s="4" t="n"/>
@@ -14019,7 +14019,7 @@
       </c>
       <c r="P177" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q177" s="4" t="n"/>
@@ -14096,7 +14096,7 @@
       </c>
       <c r="P178" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q178" s="4" t="n"/>
@@ -14175,7 +14175,7 @@
       </c>
       <c r="P179" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q179" s="4" t="n"/>
@@ -14254,7 +14254,7 @@
       </c>
       <c r="P180" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q180" s="4" t="n"/>
@@ -14333,7 +14333,7 @@
       </c>
       <c r="P181" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q181" s="4" t="n"/>
@@ -14412,7 +14412,7 @@
       </c>
       <c r="P182" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q182" s="4" t="n"/>
@@ -14491,7 +14491,7 @@
       </c>
       <c r="P183" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q183" s="4" t="n"/>
@@ -14570,7 +14570,7 @@
       </c>
       <c r="P184" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q184" s="4" t="n"/>
@@ -14649,7 +14649,7 @@
       </c>
       <c r="P185" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q185" s="4" t="n"/>
@@ -14728,7 +14728,7 @@
       </c>
       <c r="P186" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q186" s="4" t="n"/>
@@ -14807,7 +14807,7 @@
       </c>
       <c r="P187" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q187" s="4" t="n"/>
@@ -14886,7 +14886,7 @@
       </c>
       <c r="P188" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q188" s="4" t="n"/>
@@ -14965,7 +14965,7 @@
       </c>
       <c r="P189" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q189" s="4" t="n"/>
@@ -15044,7 +15044,7 @@
       </c>
       <c r="P190" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q190" s="4" t="n"/>
@@ -15123,7 +15123,7 @@
       </c>
       <c r="P191" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q191" s="4" t="n"/>
@@ -15202,7 +15202,7 @@
       </c>
       <c r="P192" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q192" s="4" t="n"/>
@@ -15281,7 +15281,7 @@
       </c>
       <c r="P193" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q193" s="4" t="n"/>
@@ -15360,7 +15360,7 @@
       </c>
       <c r="P194" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q194" s="4" t="n"/>
@@ -15439,7 +15439,7 @@
       </c>
       <c r="P195" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q195" s="4" t="n"/>
@@ -15518,7 +15518,7 @@
       </c>
       <c r="P196" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q196" s="4" t="n"/>
@@ -15597,7 +15597,7 @@
       </c>
       <c r="P197" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q197" s="4" t="n"/>
@@ -15676,7 +15676,7 @@
       </c>
       <c r="P198" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q198" s="4" t="n"/>
@@ -15755,7 +15755,7 @@
       </c>
       <c r="P199" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q199" s="4" t="n"/>
@@ -15834,7 +15834,7 @@
       </c>
       <c r="P200" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q200" s="4" t="n"/>
@@ -15913,7 +15913,7 @@
       </c>
       <c r="P201" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q201" s="4" t="n"/>
@@ -15992,7 +15992,7 @@
       </c>
       <c r="P202" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q202" s="4" t="n"/>
@@ -16071,7 +16071,7 @@
       </c>
       <c r="P203" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q203" s="4" t="n"/>
@@ -16148,7 +16148,7 @@
       </c>
       <c r="P204" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q204" s="4" t="n"/>
@@ -16225,7 +16225,7 @@
       </c>
       <c r="P205" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q205" s="4" t="n"/>
@@ -16302,7 +16302,7 @@
       </c>
       <c r="P206" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q206" s="4" t="n"/>
@@ -16379,7 +16379,7 @@
       </c>
       <c r="P207" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q207" s="4" t="n"/>
@@ -16456,7 +16456,7 @@
       </c>
       <c r="P208" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q208" s="4" t="n"/>
@@ -16533,7 +16533,7 @@
       </c>
       <c r="P209" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q209" s="4" t="n"/>
@@ -16610,7 +16610,7 @@
       </c>
       <c r="P210" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q210" s="4" t="n"/>
@@ -16687,7 +16687,7 @@
       </c>
       <c r="P211" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q211" s="4" t="n"/>
@@ -16764,7 +16764,7 @@
       </c>
       <c r="P212" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q212" s="4" t="n"/>
@@ -16841,7 +16841,7 @@
       </c>
       <c r="P213" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q213" s="4" t="n"/>
@@ -16918,7 +16918,7 @@
       </c>
       <c r="P214" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q214" s="4" t="n"/>
@@ -16995,7 +16995,7 @@
       </c>
       <c r="P215" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q215" s="4" t="n"/>
@@ -17072,7 +17072,7 @@
       </c>
       <c r="P216" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q216" s="4" t="n"/>
@@ -17149,7 +17149,7 @@
       </c>
       <c r="P217" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q217" s="4" t="n"/>
@@ -17226,7 +17226,7 @@
       </c>
       <c r="P218" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q218" s="4" t="n"/>
@@ -17303,7 +17303,7 @@
       </c>
       <c r="P219" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q219" s="4" t="n"/>
@@ -17380,7 +17380,7 @@
       </c>
       <c r="P220" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q220" s="4" t="n"/>
@@ -17457,7 +17457,7 @@
       </c>
       <c r="P221" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q221" s="4" t="n"/>
@@ -17534,7 +17534,7 @@
       </c>
       <c r="P222" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q222" s="4" t="n"/>
@@ -17611,7 +17611,7 @@
       </c>
       <c r="P223" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q223" s="4" t="n"/>
@@ -17688,7 +17688,7 @@
       </c>
       <c r="P224" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q224" s="4" t="n"/>
@@ -17765,7 +17765,7 @@
       </c>
       <c r="P225" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q225" s="4" t="n"/>
@@ -17842,7 +17842,7 @@
       </c>
       <c r="P226" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q226" s="4" t="n"/>
@@ -17919,7 +17919,7 @@
       </c>
       <c r="P227" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q227" s="4" t="n"/>
@@ -17996,7 +17996,7 @@
       </c>
       <c r="P228" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q228" s="4" t="n"/>
@@ -18073,7 +18073,7 @@
       </c>
       <c r="P229" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q229" s="4" t="n"/>
@@ -18150,7 +18150,7 @@
       </c>
       <c r="P230" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q230" s="4" t="n"/>
@@ -18227,7 +18227,7 @@
       </c>
       <c r="P231" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q231" s="4" t="n"/>
@@ -18304,7 +18304,7 @@
       </c>
       <c r="P232" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q232" s="4" t="n"/>
@@ -18381,7 +18381,7 @@
       </c>
       <c r="P233" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q233" s="4" t="n"/>
@@ -18458,7 +18458,7 @@
       </c>
       <c r="P234" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q234" s="4" t="n"/>
@@ -18537,7 +18537,7 @@
       </c>
       <c r="P235" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q235" s="4" t="n"/>
@@ -18614,7 +18614,7 @@
       </c>
       <c r="P236" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q236" s="4" t="n"/>
@@ -18693,7 +18693,7 @@
       </c>
       <c r="P237" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q237" s="4" t="n"/>
@@ -18772,7 +18772,7 @@
       </c>
       <c r="P238" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q238" s="4" t="n"/>
@@ -18851,7 +18851,7 @@
       </c>
       <c r="P239" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q239" s="4" t="n"/>
@@ -18930,7 +18930,7 @@
       </c>
       <c r="P240" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q240" s="4" t="n"/>
@@ -19009,7 +19009,7 @@
       </c>
       <c r="P241" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q241" s="4" t="n"/>
@@ -19088,7 +19088,7 @@
       </c>
       <c r="P242" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q242" s="4" t="n"/>
@@ -19167,7 +19167,7 @@
       </c>
       <c r="P243" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q243" s="4" t="n"/>
@@ -19246,7 +19246,7 @@
       </c>
       <c r="P244" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q244" s="4" t="n"/>
@@ -19325,7 +19325,7 @@
       </c>
       <c r="P245" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q245" s="4" t="n"/>
@@ -19404,7 +19404,7 @@
       </c>
       <c r="P246" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q246" s="4" t="n"/>
@@ -19483,7 +19483,7 @@
       </c>
       <c r="P247" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q247" s="4" t="n"/>
@@ -19562,7 +19562,7 @@
       </c>
       <c r="P248" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q248" s="4" t="n"/>
@@ -19641,7 +19641,7 @@
       </c>
       <c r="P249" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q249" s="4" t="n"/>
@@ -19720,7 +19720,7 @@
       </c>
       <c r="P250" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q250" s="4" t="n"/>
@@ -19799,7 +19799,7 @@
       </c>
       <c r="P251" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q251" s="4" t="n"/>
@@ -19878,7 +19878,7 @@
       </c>
       <c r="P252" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q252" s="4" t="n"/>
@@ -19957,7 +19957,7 @@
       </c>
       <c r="P253" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q253" s="4" t="n"/>
@@ -20036,7 +20036,7 @@
       </c>
       <c r="P254" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q254" s="4" t="n"/>
@@ -20115,7 +20115,7 @@
       </c>
       <c r="P255" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q255" s="4" t="n"/>
@@ -20194,7 +20194,7 @@
       </c>
       <c r="P256" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q256" s="4" t="n"/>
@@ -20273,7 +20273,7 @@
       </c>
       <c r="P257" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q257" s="4" t="n"/>
@@ -20352,7 +20352,7 @@
       </c>
       <c r="P258" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q258" s="4" t="n"/>
@@ -20431,7 +20431,7 @@
       </c>
       <c r="P259" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q259" s="4" t="n"/>
@@ -20510,7 +20510,7 @@
       </c>
       <c r="P260" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q260" s="4" t="n"/>
@@ -20589,7 +20589,7 @@
       </c>
       <c r="P261" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q261" s="4" t="n"/>
@@ -20666,7 +20666,7 @@
       </c>
       <c r="P262" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q262" s="4" t="n"/>
@@ -20743,7 +20743,7 @@
       </c>
       <c r="P263" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q263" s="4" t="n"/>
@@ -20822,7 +20822,7 @@
       </c>
       <c r="P264" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q264" s="4" t="n"/>
@@ -20901,7 +20901,7 @@
       </c>
       <c r="P265" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q265" s="4" t="n"/>
@@ -20980,7 +20980,7 @@
       </c>
       <c r="P266" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q266" s="4" t="n"/>
@@ -21059,7 +21059,7 @@
       </c>
       <c r="P267" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q267" s="4" t="n"/>
@@ -21138,7 +21138,7 @@
       </c>
       <c r="P268" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q268" s="4" t="n"/>
@@ -21217,7 +21217,7 @@
       </c>
       <c r="P269" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q269" s="4" t="n"/>
@@ -21294,7 +21294,7 @@
       </c>
       <c r="P270" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q270" s="4" t="n"/>
@@ -21379,7 +21379,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
     </row>

--- a/assets/data/world-bank/excel/ove_banco_mundial_venezuela_infraestructura_y_digitalizacion.xlsx
+++ b/assets/data/world-bank/excel/ove_banco_mundial_venezuela_infraestructura_y_digitalizacion.xlsx
@@ -715,7 +715,7 @@
       </c>
       <c r="P7" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q7" s="4" t="n"/>
@@ -792,7 +792,7 @@
       </c>
       <c r="P8" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q8" s="4" t="n"/>
@@ -869,7 +869,7 @@
       </c>
       <c r="P9" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q9" s="4" t="n"/>
@@ -946,7 +946,7 @@
       </c>
       <c r="P10" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q10" s="4" t="n"/>
@@ -1023,7 +1023,7 @@
       </c>
       <c r="P11" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q11" s="4" t="n"/>
@@ -1100,7 +1100,7 @@
       </c>
       <c r="P12" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q12" s="4" t="n"/>
@@ -1177,7 +1177,7 @@
       </c>
       <c r="P13" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q13" s="4" t="n"/>
@@ -1254,7 +1254,7 @@
       </c>
       <c r="P14" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q14" s="4" t="n"/>
@@ -1331,7 +1331,7 @@
       </c>
       <c r="P15" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q15" s="4" t="n"/>
@@ -1408,7 +1408,7 @@
       </c>
       <c r="P16" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q16" s="4" t="n"/>
@@ -1487,7 +1487,7 @@
       </c>
       <c r="P17" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q17" s="4" t="n"/>
@@ -1566,7 +1566,7 @@
       </c>
       <c r="P18" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q18" s="4" t="n"/>
@@ -1645,7 +1645,7 @@
       </c>
       <c r="P19" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q19" s="4" t="n"/>
@@ -1724,7 +1724,7 @@
       </c>
       <c r="P20" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q20" s="4" t="n"/>
@@ -1803,7 +1803,7 @@
       </c>
       <c r="P21" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q21" s="4" t="n"/>
@@ -1882,7 +1882,7 @@
       </c>
       <c r="P22" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q22" s="4" t="n"/>
@@ -1961,7 +1961,7 @@
       </c>
       <c r="P23" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q23" s="4" t="n"/>
@@ -2040,7 +2040,7 @@
       </c>
       <c r="P24" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q24" s="4" t="n"/>
@@ -2119,7 +2119,7 @@
       </c>
       <c r="P25" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q25" s="4" t="n"/>
@@ -2198,7 +2198,7 @@
       </c>
       <c r="P26" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q26" s="4" t="n"/>
@@ -2277,7 +2277,7 @@
       </c>
       <c r="P27" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q27" s="4" t="n"/>
@@ -2356,7 +2356,7 @@
       </c>
       <c r="P28" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q28" s="4" t="n"/>
@@ -2435,7 +2435,7 @@
       </c>
       <c r="P29" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q29" s="4" t="n"/>
@@ -2514,7 +2514,7 @@
       </c>
       <c r="P30" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q30" s="4" t="n"/>
@@ -2593,7 +2593,7 @@
       </c>
       <c r="P31" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q31" s="4" t="n"/>
@@ -2672,7 +2672,7 @@
       </c>
       <c r="P32" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q32" s="4" t="n"/>
@@ -2751,7 +2751,7 @@
       </c>
       <c r="P33" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q33" s="4" t="n"/>
@@ -2830,7 +2830,7 @@
       </c>
       <c r="P34" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q34" s="4" t="n"/>
@@ -2909,7 +2909,7 @@
       </c>
       <c r="P35" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q35" s="4" t="n"/>
@@ -2988,7 +2988,7 @@
       </c>
       <c r="P36" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q36" s="4" t="n"/>
@@ -3067,7 +3067,7 @@
       </c>
       <c r="P37" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q37" s="4" t="n"/>
@@ -3146,7 +3146,7 @@
       </c>
       <c r="P38" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q38" s="4" t="n"/>
@@ -3225,7 +3225,7 @@
       </c>
       <c r="P39" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q39" s="4" t="n"/>
@@ -3304,7 +3304,7 @@
       </c>
       <c r="P40" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q40" s="4" t="n"/>
@@ -3383,7 +3383,7 @@
       </c>
       <c r="P41" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q41" s="4" t="n"/>
@@ -3462,7 +3462,7 @@
       </c>
       <c r="P42" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q42" s="4" t="n"/>
@@ -3541,7 +3541,7 @@
       </c>
       <c r="P43" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q43" s="4" t="n"/>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="P44" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q44" s="4" t="n"/>
@@ -3699,7 +3699,7 @@
       </c>
       <c r="P45" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q45" s="4" t="n"/>
@@ -3778,7 +3778,7 @@
       </c>
       <c r="P46" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q46" s="4" t="n"/>
@@ -3857,7 +3857,7 @@
       </c>
       <c r="P47" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q47" s="4" t="n"/>
@@ -3936,7 +3936,7 @@
       </c>
       <c r="P48" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q48" s="4" t="n"/>
@@ -4015,7 +4015,7 @@
       </c>
       <c r="P49" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q49" s="4" t="n"/>
@@ -4094,7 +4094,7 @@
       </c>
       <c r="P50" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q50" s="4" t="n"/>
@@ -4173,7 +4173,7 @@
       </c>
       <c r="P51" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q51" s="4" t="n"/>
@@ -4252,7 +4252,7 @@
       </c>
       <c r="P52" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q52" s="4" t="n"/>
@@ -4331,7 +4331,7 @@
       </c>
       <c r="P53" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q53" s="4" t="n"/>
@@ -4410,7 +4410,7 @@
       </c>
       <c r="P54" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q54" s="4" t="n"/>
@@ -4489,7 +4489,7 @@
       </c>
       <c r="P55" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q55" s="4" t="n"/>
@@ -4568,7 +4568,7 @@
       </c>
       <c r="P56" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q56" s="4" t="n"/>
@@ -4647,7 +4647,7 @@
       </c>
       <c r="P57" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q57" s="4" t="n"/>
@@ -4726,7 +4726,7 @@
       </c>
       <c r="P58" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q58" s="4" t="n"/>
@@ -4805,7 +4805,7 @@
       </c>
       <c r="P59" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q59" s="4" t="n"/>
@@ -4884,7 +4884,7 @@
       </c>
       <c r="P60" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q60" s="4" t="n"/>
@@ -4963,7 +4963,7 @@
       </c>
       <c r="P61" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q61" s="4" t="n"/>
@@ -5042,7 +5042,7 @@
       </c>
       <c r="P62" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q62" s="4" t="n"/>
@@ -5121,7 +5121,7 @@
       </c>
       <c r="P63" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q63" s="4" t="n"/>
@@ -5200,7 +5200,7 @@
       </c>
       <c r="P64" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q64" s="4" t="n"/>
@@ -5279,7 +5279,7 @@
       </c>
       <c r="P65" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q65" s="4" t="n"/>
@@ -5358,7 +5358,7 @@
       </c>
       <c r="P66" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q66" s="4" t="n"/>
@@ -5437,7 +5437,7 @@
       </c>
       <c r="P67" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q67" s="4" t="n"/>
@@ -5516,7 +5516,7 @@
       </c>
       <c r="P68" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q68" s="4" t="n"/>
@@ -5595,7 +5595,7 @@
       </c>
       <c r="P69" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q69" s="4" t="n"/>
@@ -5674,7 +5674,7 @@
       </c>
       <c r="P70" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q70" s="4" t="n"/>
@@ -5751,7 +5751,7 @@
       </c>
       <c r="P71" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q71" s="4" t="n"/>
@@ -5828,7 +5828,7 @@
       </c>
       <c r="P72" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q72" s="4" t="n"/>
@@ -5907,7 +5907,7 @@
       </c>
       <c r="P73" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q73" s="4" t="n"/>
@@ -5984,7 +5984,7 @@
       </c>
       <c r="P74" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q74" s="4" t="n"/>
@@ -6061,7 +6061,7 @@
       </c>
       <c r="P75" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q75" s="4" t="n"/>
@@ -6138,7 +6138,7 @@
       </c>
       <c r="P76" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q76" s="4" t="n"/>
@@ -6215,7 +6215,7 @@
       </c>
       <c r="P77" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q77" s="4" t="n"/>
@@ -6294,7 +6294,7 @@
       </c>
       <c r="P78" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q78" s="4" t="n"/>
@@ -6371,7 +6371,7 @@
       </c>
       <c r="P79" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q79" s="4" t="n"/>
@@ -6448,7 +6448,7 @@
       </c>
       <c r="P80" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q80" s="4" t="n"/>
@@ -6525,7 +6525,7 @@
       </c>
       <c r="P81" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q81" s="4" t="n"/>
@@ -6602,7 +6602,7 @@
       </c>
       <c r="P82" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q82" s="4" t="n"/>
@@ -6681,7 +6681,7 @@
       </c>
       <c r="P83" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q83" s="4" t="n"/>
@@ -6758,7 +6758,7 @@
       </c>
       <c r="P84" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q84" s="4" t="n"/>
@@ -6835,7 +6835,7 @@
       </c>
       <c r="P85" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q85" s="4" t="n"/>
@@ -6912,7 +6912,7 @@
       </c>
       <c r="P86" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q86" s="4" t="n"/>
@@ -6989,7 +6989,7 @@
       </c>
       <c r="P87" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q87" s="4" t="n"/>
@@ -7068,7 +7068,7 @@
       </c>
       <c r="P88" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q88" s="4" t="n"/>
@@ -7147,7 +7147,7 @@
       </c>
       <c r="P89" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q89" s="4" t="n"/>
@@ -7226,7 +7226,7 @@
       </c>
       <c r="P90" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q90" s="4" t="n"/>
@@ -7305,7 +7305,7 @@
       </c>
       <c r="P91" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q91" s="4" t="n"/>
@@ -7384,7 +7384,7 @@
       </c>
       <c r="P92" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q92" s="4" t="n"/>
@@ -7463,7 +7463,7 @@
       </c>
       <c r="P93" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q93" s="4" t="n"/>
@@ -7542,7 +7542,7 @@
       </c>
       <c r="P94" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q94" s="4" t="n"/>
@@ -7621,7 +7621,7 @@
       </c>
       <c r="P95" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q95" s="4" t="n"/>
@@ -7700,7 +7700,7 @@
       </c>
       <c r="P96" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q96" s="4" t="n"/>
@@ -7779,7 +7779,7 @@
       </c>
       <c r="P97" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q97" s="4" t="n"/>
@@ -7858,7 +7858,7 @@
       </c>
       <c r="P98" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q98" s="4" t="n"/>
@@ -7937,7 +7937,7 @@
       </c>
       <c r="P99" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q99" s="4" t="n"/>
@@ -8016,7 +8016,7 @@
       </c>
       <c r="P100" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q100" s="4" t="n"/>
@@ -8095,7 +8095,7 @@
       </c>
       <c r="P101" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q101" s="4" t="n"/>
@@ -8174,7 +8174,7 @@
       </c>
       <c r="P102" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q102" s="4" t="n"/>
@@ -8253,7 +8253,7 @@
       </c>
       <c r="P103" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q103" s="4" t="n"/>
@@ -8332,7 +8332,7 @@
       </c>
       <c r="P104" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q104" s="4" t="n"/>
@@ -8411,7 +8411,7 @@
       </c>
       <c r="P105" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q105" s="4" t="n"/>
@@ -8490,7 +8490,7 @@
       </c>
       <c r="P106" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q106" s="4" t="n"/>
@@ -8569,7 +8569,7 @@
       </c>
       <c r="P107" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q107" s="4" t="n"/>
@@ -8648,7 +8648,7 @@
       </c>
       <c r="P108" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q108" s="4" t="n"/>
@@ -8727,7 +8727,7 @@
       </c>
       <c r="P109" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q109" s="4" t="n"/>
@@ -8806,7 +8806,7 @@
       </c>
       <c r="P110" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q110" s="4" t="n"/>
@@ -8885,7 +8885,7 @@
       </c>
       <c r="P111" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q111" s="4" t="n"/>
@@ -8964,7 +8964,7 @@
       </c>
       <c r="P112" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q112" s="4" t="n"/>
@@ -9043,7 +9043,7 @@
       </c>
       <c r="P113" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q113" s="4" t="n"/>
@@ -9122,7 +9122,7 @@
       </c>
       <c r="P114" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q114" s="4" t="n"/>
@@ -9201,7 +9201,7 @@
       </c>
       <c r="P115" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q115" s="4" t="n"/>
@@ -9280,7 +9280,7 @@
       </c>
       <c r="P116" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q116" s="4" t="n"/>
@@ -9359,7 +9359,7 @@
       </c>
       <c r="P117" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q117" s="4" t="n"/>
@@ -9438,7 +9438,7 @@
       </c>
       <c r="P118" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q118" s="4" t="n"/>
@@ -9517,7 +9517,7 @@
       </c>
       <c r="P119" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q119" s="4" t="n"/>
@@ -9596,7 +9596,7 @@
       </c>
       <c r="P120" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q120" s="4" t="n"/>
@@ -9675,7 +9675,7 @@
       </c>
       <c r="P121" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q121" s="4" t="n"/>
@@ -9754,7 +9754,7 @@
       </c>
       <c r="P122" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q122" s="4" t="n"/>
@@ -9833,7 +9833,7 @@
       </c>
       <c r="P123" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q123" s="4" t="n"/>
@@ -9912,7 +9912,7 @@
       </c>
       <c r="P124" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q124" s="4" t="n"/>
@@ -9991,7 +9991,7 @@
       </c>
       <c r="P125" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q125" s="4" t="n"/>
@@ -10070,7 +10070,7 @@
       </c>
       <c r="P126" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q126" s="4" t="n"/>
@@ -10149,7 +10149,7 @@
       </c>
       <c r="P127" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q127" s="4" t="n"/>
@@ -10228,7 +10228,7 @@
       </c>
       <c r="P128" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q128" s="4" t="n"/>
@@ -10307,7 +10307,7 @@
       </c>
       <c r="P129" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q129" s="4" t="n"/>
@@ -10386,7 +10386,7 @@
       </c>
       <c r="P130" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q130" s="4" t="n"/>
@@ -10465,7 +10465,7 @@
       </c>
       <c r="P131" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q131" s="4" t="n"/>
@@ -10544,7 +10544,7 @@
       </c>
       <c r="P132" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q132" s="4" t="n"/>
@@ -10623,7 +10623,7 @@
       </c>
       <c r="P133" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q133" s="4" t="n"/>
@@ -10702,7 +10702,7 @@
       </c>
       <c r="P134" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q134" s="4" t="n"/>
@@ -10781,7 +10781,7 @@
       </c>
       <c r="P135" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q135" s="4" t="n"/>
@@ -10860,7 +10860,7 @@
       </c>
       <c r="P136" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q136" s="4" t="n"/>
@@ -10939,7 +10939,7 @@
       </c>
       <c r="P137" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q137" s="4" t="n"/>
@@ -11016,7 +11016,7 @@
       </c>
       <c r="P138" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q138" s="4" t="n"/>
@@ -11093,7 +11093,7 @@
       </c>
       <c r="P139" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q139" s="4" t="n"/>
@@ -11170,7 +11170,7 @@
       </c>
       <c r="P140" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q140" s="4" t="n"/>
@@ -11247,7 +11247,7 @@
       </c>
       <c r="P141" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q141" s="4" t="n"/>
@@ -11324,7 +11324,7 @@
       </c>
       <c r="P142" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q142" s="4" t="n"/>
@@ -11401,7 +11401,7 @@
       </c>
       <c r="P143" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q143" s="4" t="n"/>
@@ -11478,7 +11478,7 @@
       </c>
       <c r="P144" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q144" s="4" t="n"/>
@@ -11555,7 +11555,7 @@
       </c>
       <c r="P145" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q145" s="4" t="n"/>
@@ -11632,7 +11632,7 @@
       </c>
       <c r="P146" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q146" s="4" t="n"/>
@@ -11709,7 +11709,7 @@
       </c>
       <c r="P147" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q147" s="4" t="n"/>
@@ -11786,7 +11786,7 @@
       </c>
       <c r="P148" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q148" s="4" t="n"/>
@@ -11863,7 +11863,7 @@
       </c>
       <c r="P149" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q149" s="4" t="n"/>
@@ -11940,7 +11940,7 @@
       </c>
       <c r="P150" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q150" s="4" t="n"/>
@@ -12017,7 +12017,7 @@
       </c>
       <c r="P151" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q151" s="4" t="n"/>
@@ -12094,7 +12094,7 @@
       </c>
       <c r="P152" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q152" s="4" t="n"/>
@@ -12171,7 +12171,7 @@
       </c>
       <c r="P153" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q153" s="4" t="n"/>
@@ -12248,7 +12248,7 @@
       </c>
       <c r="P154" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q154" s="4" t="n"/>
@@ -12325,7 +12325,7 @@
       </c>
       <c r="P155" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q155" s="4" t="n"/>
@@ -12402,7 +12402,7 @@
       </c>
       <c r="P156" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q156" s="4" t="n"/>
@@ -12479,7 +12479,7 @@
       </c>
       <c r="P157" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q157" s="4" t="n"/>
@@ -12556,7 +12556,7 @@
       </c>
       <c r="P158" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q158" s="4" t="n"/>
@@ -12633,7 +12633,7 @@
       </c>
       <c r="P159" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q159" s="4" t="n"/>
@@ -12710,7 +12710,7 @@
       </c>
       <c r="P160" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q160" s="4" t="n"/>
@@ -12787,7 +12787,7 @@
       </c>
       <c r="P161" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q161" s="4" t="n"/>
@@ -12864,7 +12864,7 @@
       </c>
       <c r="P162" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q162" s="4" t="n"/>
@@ -12941,7 +12941,7 @@
       </c>
       <c r="P163" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q163" s="4" t="n"/>
@@ -13018,7 +13018,7 @@
       </c>
       <c r="P164" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q164" s="4" t="n"/>
@@ -13095,7 +13095,7 @@
       </c>
       <c r="P165" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q165" s="4" t="n"/>
@@ -13172,7 +13172,7 @@
       </c>
       <c r="P166" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q166" s="4" t="n"/>
@@ -13249,7 +13249,7 @@
       </c>
       <c r="P167" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q167" s="4" t="n"/>
@@ -13326,7 +13326,7 @@
       </c>
       <c r="P168" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q168" s="4" t="n"/>
@@ -13403,7 +13403,7 @@
       </c>
       <c r="P169" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q169" s="4" t="n"/>
@@ -13480,7 +13480,7 @@
       </c>
       <c r="P170" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q170" s="4" t="n"/>
@@ -13557,7 +13557,7 @@
       </c>
       <c r="P171" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q171" s="4" t="n"/>
@@ -13634,7 +13634,7 @@
       </c>
       <c r="P172" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q172" s="4" t="n"/>
@@ -13711,7 +13711,7 @@
       </c>
       <c r="P173" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q173" s="4" t="n"/>
@@ -13788,7 +13788,7 @@
       </c>
       <c r="P174" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q174" s="4" t="n"/>
@@ -13865,7 +13865,7 @@
       </c>
       <c r="P175" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q175" s="4" t="n"/>
@@ -13942,7 +13942,7 @@
       </c>
       <c r="P176" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q176" s="4" t="n"/>
@@ -14019,7 +14019,7 @@
       </c>
       <c r="P177" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q177" s="4" t="n"/>
@@ -14096,7 +14096,7 @@
       </c>
       <c r="P178" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q178" s="4" t="n"/>
@@ -14175,7 +14175,7 @@
       </c>
       <c r="P179" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q179" s="4" t="n"/>
@@ -14254,7 +14254,7 @@
       </c>
       <c r="P180" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q180" s="4" t="n"/>
@@ -14333,7 +14333,7 @@
       </c>
       <c r="P181" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q181" s="4" t="n"/>
@@ -14412,7 +14412,7 @@
       </c>
       <c r="P182" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q182" s="4" t="n"/>
@@ -14491,7 +14491,7 @@
       </c>
       <c r="P183" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q183" s="4" t="n"/>
@@ -14570,7 +14570,7 @@
       </c>
       <c r="P184" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q184" s="4" t="n"/>
@@ -14649,7 +14649,7 @@
       </c>
       <c r="P185" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q185" s="4" t="n"/>
@@ -14728,7 +14728,7 @@
       </c>
       <c r="P186" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q186" s="4" t="n"/>
@@ -14807,7 +14807,7 @@
       </c>
       <c r="P187" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q187" s="4" t="n"/>
@@ -14886,7 +14886,7 @@
       </c>
       <c r="P188" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q188" s="4" t="n"/>
@@ -14965,7 +14965,7 @@
       </c>
       <c r="P189" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q189" s="4" t="n"/>
@@ -15044,7 +15044,7 @@
       </c>
       <c r="P190" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q190" s="4" t="n"/>
@@ -15123,7 +15123,7 @@
       </c>
       <c r="P191" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q191" s="4" t="n"/>
@@ -15202,7 +15202,7 @@
       </c>
       <c r="P192" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q192" s="4" t="n"/>
@@ -15281,7 +15281,7 @@
       </c>
       <c r="P193" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q193" s="4" t="n"/>
@@ -15360,7 +15360,7 @@
       </c>
       <c r="P194" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q194" s="4" t="n"/>
@@ -15439,7 +15439,7 @@
       </c>
       <c r="P195" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q195" s="4" t="n"/>
@@ -15518,7 +15518,7 @@
       </c>
       <c r="P196" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q196" s="4" t="n"/>
@@ -15597,7 +15597,7 @@
       </c>
       <c r="P197" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q197" s="4" t="n"/>
@@ -15676,7 +15676,7 @@
       </c>
       <c r="P198" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q198" s="4" t="n"/>
@@ -15755,7 +15755,7 @@
       </c>
       <c r="P199" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q199" s="4" t="n"/>
@@ -15834,7 +15834,7 @@
       </c>
       <c r="P200" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q200" s="4" t="n"/>
@@ -15913,7 +15913,7 @@
       </c>
       <c r="P201" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q201" s="4" t="n"/>
@@ -15992,7 +15992,7 @@
       </c>
       <c r="P202" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q202" s="4" t="n"/>
@@ -16071,7 +16071,7 @@
       </c>
       <c r="P203" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q203" s="4" t="n"/>
@@ -16148,7 +16148,7 @@
       </c>
       <c r="P204" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q204" s="4" t="n"/>
@@ -16225,7 +16225,7 @@
       </c>
       <c r="P205" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q205" s="4" t="n"/>
@@ -16302,7 +16302,7 @@
       </c>
       <c r="P206" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q206" s="4" t="n"/>
@@ -16379,7 +16379,7 @@
       </c>
       <c r="P207" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q207" s="4" t="n"/>
@@ -16456,7 +16456,7 @@
       </c>
       <c r="P208" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q208" s="4" t="n"/>
@@ -16533,7 +16533,7 @@
       </c>
       <c r="P209" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q209" s="4" t="n"/>
@@ -16610,7 +16610,7 @@
       </c>
       <c r="P210" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q210" s="4" t="n"/>
@@ -16687,7 +16687,7 @@
       </c>
       <c r="P211" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q211" s="4" t="n"/>
@@ -16764,7 +16764,7 @@
       </c>
       <c r="P212" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q212" s="4" t="n"/>
@@ -16841,7 +16841,7 @@
       </c>
       <c r="P213" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q213" s="4" t="n"/>
@@ -16918,7 +16918,7 @@
       </c>
       <c r="P214" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q214" s="4" t="n"/>
@@ -16995,7 +16995,7 @@
       </c>
       <c r="P215" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q215" s="4" t="n"/>
@@ -17072,7 +17072,7 @@
       </c>
       <c r="P216" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q216" s="4" t="n"/>
@@ -17149,7 +17149,7 @@
       </c>
       <c r="P217" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q217" s="4" t="n"/>
@@ -17226,7 +17226,7 @@
       </c>
       <c r="P218" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q218" s="4" t="n"/>
@@ -17303,7 +17303,7 @@
       </c>
       <c r="P219" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q219" s="4" t="n"/>
@@ -17380,7 +17380,7 @@
       </c>
       <c r="P220" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q220" s="4" t="n"/>
@@ -17457,7 +17457,7 @@
       </c>
       <c r="P221" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q221" s="4" t="n"/>
@@ -17534,7 +17534,7 @@
       </c>
       <c r="P222" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q222" s="4" t="n"/>
@@ -17611,7 +17611,7 @@
       </c>
       <c r="P223" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q223" s="4" t="n"/>
@@ -17688,7 +17688,7 @@
       </c>
       <c r="P224" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q224" s="4" t="n"/>
@@ -17765,7 +17765,7 @@
       </c>
       <c r="P225" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q225" s="4" t="n"/>
@@ -17842,7 +17842,7 @@
       </c>
       <c r="P226" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q226" s="4" t="n"/>
@@ -17919,7 +17919,7 @@
       </c>
       <c r="P227" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q227" s="4" t="n"/>
@@ -17996,7 +17996,7 @@
       </c>
       <c r="P228" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q228" s="4" t="n"/>
@@ -18073,7 +18073,7 @@
       </c>
       <c r="P229" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q229" s="4" t="n"/>
@@ -18150,7 +18150,7 @@
       </c>
       <c r="P230" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q230" s="4" t="n"/>
@@ -18227,7 +18227,7 @@
       </c>
       <c r="P231" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q231" s="4" t="n"/>
@@ -18304,7 +18304,7 @@
       </c>
       <c r="P232" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q232" s="4" t="n"/>
@@ -18381,7 +18381,7 @@
       </c>
       <c r="P233" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q233" s="4" t="n"/>
@@ -18458,7 +18458,7 @@
       </c>
       <c r="P234" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q234" s="4" t="n"/>
@@ -18537,7 +18537,7 @@
       </c>
       <c r="P235" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q235" s="4" t="n"/>
@@ -18614,7 +18614,7 @@
       </c>
       <c r="P236" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q236" s="4" t="n"/>
@@ -18693,7 +18693,7 @@
       </c>
       <c r="P237" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q237" s="4" t="n"/>
@@ -18772,7 +18772,7 @@
       </c>
       <c r="P238" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q238" s="4" t="n"/>
@@ -18851,7 +18851,7 @@
       </c>
       <c r="P239" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q239" s="4" t="n"/>
@@ -18930,7 +18930,7 @@
       </c>
       <c r="P240" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q240" s="4" t="n"/>
@@ -19009,7 +19009,7 @@
       </c>
       <c r="P241" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q241" s="4" t="n"/>
@@ -19088,7 +19088,7 @@
       </c>
       <c r="P242" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q242" s="4" t="n"/>
@@ -19167,7 +19167,7 @@
       </c>
       <c r="P243" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q243" s="4" t="n"/>
@@ -19246,7 +19246,7 @@
       </c>
       <c r="P244" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q244" s="4" t="n"/>
@@ -19325,7 +19325,7 @@
       </c>
       <c r="P245" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q245" s="4" t="n"/>
@@ -19404,7 +19404,7 @@
       </c>
       <c r="P246" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q246" s="4" t="n"/>
@@ -19483,7 +19483,7 @@
       </c>
       <c r="P247" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q247" s="4" t="n"/>
@@ -19562,7 +19562,7 @@
       </c>
       <c r="P248" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q248" s="4" t="n"/>
@@ -19641,7 +19641,7 @@
       </c>
       <c r="P249" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q249" s="4" t="n"/>
@@ -19720,7 +19720,7 @@
       </c>
       <c r="P250" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q250" s="4" t="n"/>
@@ -19799,7 +19799,7 @@
       </c>
       <c r="P251" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q251" s="4" t="n"/>
@@ -19878,7 +19878,7 @@
       </c>
       <c r="P252" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q252" s="4" t="n"/>
@@ -19957,7 +19957,7 @@
       </c>
       <c r="P253" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q253" s="4" t="n"/>
@@ -20036,7 +20036,7 @@
       </c>
       <c r="P254" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q254" s="4" t="n"/>
@@ -20115,7 +20115,7 @@
       </c>
       <c r="P255" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q255" s="4" t="n"/>
@@ -20194,7 +20194,7 @@
       </c>
       <c r="P256" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q256" s="4" t="n"/>
@@ -20273,7 +20273,7 @@
       </c>
       <c r="P257" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q257" s="4" t="n"/>
@@ -20352,7 +20352,7 @@
       </c>
       <c r="P258" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q258" s="4" t="n"/>
@@ -20431,7 +20431,7 @@
       </c>
       <c r="P259" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q259" s="4" t="n"/>
@@ -20510,7 +20510,7 @@
       </c>
       <c r="P260" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q260" s="4" t="n"/>
@@ -20589,7 +20589,7 @@
       </c>
       <c r="P261" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q261" s="4" t="n"/>
@@ -20666,7 +20666,7 @@
       </c>
       <c r="P262" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q262" s="4" t="n"/>
@@ -20743,7 +20743,7 @@
       </c>
       <c r="P263" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q263" s="4" t="n"/>
@@ -20822,7 +20822,7 @@
       </c>
       <c r="P264" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q264" s="4" t="n"/>
@@ -20901,7 +20901,7 @@
       </c>
       <c r="P265" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q265" s="4" t="n"/>
@@ -20980,7 +20980,7 @@
       </c>
       <c r="P266" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q266" s="4" t="n"/>
@@ -21059,7 +21059,7 @@
       </c>
       <c r="P267" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q267" s="4" t="n"/>
@@ -21138,7 +21138,7 @@
       </c>
       <c r="P268" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q268" s="4" t="n"/>
@@ -21217,7 +21217,7 @@
       </c>
       <c r="P269" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q269" s="4" t="n"/>
@@ -21294,7 +21294,7 @@
       </c>
       <c r="P270" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q270" s="4" t="n"/>
@@ -21379,7 +21379,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>

--- a/assets/data/world-bank/excel/ove_banco_mundial_venezuela_infraestructura_y_digitalizacion.xlsx
+++ b/assets/data/world-bank/excel/ove_banco_mundial_venezuela_infraestructura_y_digitalizacion.xlsx
@@ -715,7 +715,7 @@
       </c>
       <c r="P7" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q7" s="4" t="n"/>
@@ -792,7 +792,7 @@
       </c>
       <c r="P8" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q8" s="4" t="n"/>
@@ -869,7 +869,7 @@
       </c>
       <c r="P9" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q9" s="4" t="n"/>
@@ -946,7 +946,7 @@
       </c>
       <c r="P10" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q10" s="4" t="n"/>
@@ -1023,7 +1023,7 @@
       </c>
       <c r="P11" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q11" s="4" t="n"/>
@@ -1100,7 +1100,7 @@
       </c>
       <c r="P12" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q12" s="4" t="n"/>
@@ -1177,7 +1177,7 @@
       </c>
       <c r="P13" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q13" s="4" t="n"/>
@@ -1254,7 +1254,7 @@
       </c>
       <c r="P14" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q14" s="4" t="n"/>
@@ -1331,7 +1331,7 @@
       </c>
       <c r="P15" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q15" s="4" t="n"/>
@@ -1408,7 +1408,7 @@
       </c>
       <c r="P16" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q16" s="4" t="n"/>
@@ -1487,7 +1487,7 @@
       </c>
       <c r="P17" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q17" s="4" t="n"/>
@@ -1566,7 +1566,7 @@
       </c>
       <c r="P18" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q18" s="4" t="n"/>
@@ -1645,7 +1645,7 @@
       </c>
       <c r="P19" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q19" s="4" t="n"/>
@@ -1724,7 +1724,7 @@
       </c>
       <c r="P20" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q20" s="4" t="n"/>
@@ -1803,7 +1803,7 @@
       </c>
       <c r="P21" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q21" s="4" t="n"/>
@@ -1882,7 +1882,7 @@
       </c>
       <c r="P22" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q22" s="4" t="n"/>
@@ -1961,7 +1961,7 @@
       </c>
       <c r="P23" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q23" s="4" t="n"/>
@@ -2040,7 +2040,7 @@
       </c>
       <c r="P24" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q24" s="4" t="n"/>
@@ -2119,7 +2119,7 @@
       </c>
       <c r="P25" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q25" s="4" t="n"/>
@@ -2198,7 +2198,7 @@
       </c>
       <c r="P26" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q26" s="4" t="n"/>
@@ -2277,7 +2277,7 @@
       </c>
       <c r="P27" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q27" s="4" t="n"/>
@@ -2356,7 +2356,7 @@
       </c>
       <c r="P28" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q28" s="4" t="n"/>
@@ -2435,7 +2435,7 @@
       </c>
       <c r="P29" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q29" s="4" t="n"/>
@@ -2514,7 +2514,7 @@
       </c>
       <c r="P30" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q30" s="4" t="n"/>
@@ -2593,7 +2593,7 @@
       </c>
       <c r="P31" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q31" s="4" t="n"/>
@@ -2672,7 +2672,7 @@
       </c>
       <c r="P32" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q32" s="4" t="n"/>
@@ -2751,7 +2751,7 @@
       </c>
       <c r="P33" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q33" s="4" t="n"/>
@@ -2830,7 +2830,7 @@
       </c>
       <c r="P34" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q34" s="4" t="n"/>
@@ -2909,7 +2909,7 @@
       </c>
       <c r="P35" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q35" s="4" t="n"/>
@@ -2988,7 +2988,7 @@
       </c>
       <c r="P36" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q36" s="4" t="n"/>
@@ -3067,7 +3067,7 @@
       </c>
       <c r="P37" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q37" s="4" t="n"/>
@@ -3146,7 +3146,7 @@
       </c>
       <c r="P38" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q38" s="4" t="n"/>
@@ -3225,7 +3225,7 @@
       </c>
       <c r="P39" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q39" s="4" t="n"/>
@@ -3304,7 +3304,7 @@
       </c>
       <c r="P40" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q40" s="4" t="n"/>
@@ -3383,7 +3383,7 @@
       </c>
       <c r="P41" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q41" s="4" t="n"/>
@@ -3462,7 +3462,7 @@
       </c>
       <c r="P42" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q42" s="4" t="n"/>
@@ -3541,7 +3541,7 @@
       </c>
       <c r="P43" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q43" s="4" t="n"/>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="P44" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q44" s="4" t="n"/>
@@ -3699,7 +3699,7 @@
       </c>
       <c r="P45" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q45" s="4" t="n"/>
@@ -3778,7 +3778,7 @@
       </c>
       <c r="P46" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q46" s="4" t="n"/>
@@ -3857,7 +3857,7 @@
       </c>
       <c r="P47" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q47" s="4" t="n"/>
@@ -3936,7 +3936,7 @@
       </c>
       <c r="P48" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q48" s="4" t="n"/>
@@ -4015,7 +4015,7 @@
       </c>
       <c r="P49" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q49" s="4" t="n"/>
@@ -4094,7 +4094,7 @@
       </c>
       <c r="P50" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q50" s="4" t="n"/>
@@ -4173,7 +4173,7 @@
       </c>
       <c r="P51" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q51" s="4" t="n"/>
@@ -4252,7 +4252,7 @@
       </c>
       <c r="P52" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q52" s="4" t="n"/>
@@ -4331,7 +4331,7 @@
       </c>
       <c r="P53" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q53" s="4" t="n"/>
@@ -4410,7 +4410,7 @@
       </c>
       <c r="P54" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q54" s="4" t="n"/>
@@ -4489,7 +4489,7 @@
       </c>
       <c r="P55" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q55" s="4" t="n"/>
@@ -4568,7 +4568,7 @@
       </c>
       <c r="P56" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q56" s="4" t="n"/>
@@ -4647,7 +4647,7 @@
       </c>
       <c r="P57" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q57" s="4" t="n"/>
@@ -4726,7 +4726,7 @@
       </c>
       <c r="P58" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q58" s="4" t="n"/>
@@ -4805,7 +4805,7 @@
       </c>
       <c r="P59" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q59" s="4" t="n"/>
@@ -4884,7 +4884,7 @@
       </c>
       <c r="P60" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q60" s="4" t="n"/>
@@ -4963,7 +4963,7 @@
       </c>
       <c r="P61" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q61" s="4" t="n"/>
@@ -5042,7 +5042,7 @@
       </c>
       <c r="P62" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q62" s="4" t="n"/>
@@ -5121,7 +5121,7 @@
       </c>
       <c r="P63" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q63" s="4" t="n"/>
@@ -5200,7 +5200,7 @@
       </c>
       <c r="P64" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q64" s="4" t="n"/>
@@ -5279,7 +5279,7 @@
       </c>
       <c r="P65" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q65" s="4" t="n"/>
@@ -5358,7 +5358,7 @@
       </c>
       <c r="P66" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q66" s="4" t="n"/>
@@ -5437,7 +5437,7 @@
       </c>
       <c r="P67" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q67" s="4" t="n"/>
@@ -5516,7 +5516,7 @@
       </c>
       <c r="P68" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q68" s="4" t="n"/>
@@ -5595,7 +5595,7 @@
       </c>
       <c r="P69" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q69" s="4" t="n"/>
@@ -5674,7 +5674,7 @@
       </c>
       <c r="P70" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q70" s="4" t="n"/>
@@ -5751,7 +5751,7 @@
       </c>
       <c r="P71" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q71" s="4" t="n"/>
@@ -5828,7 +5828,7 @@
       </c>
       <c r="P72" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q72" s="4" t="n"/>
@@ -5907,7 +5907,7 @@
       </c>
       <c r="P73" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q73" s="4" t="n"/>
@@ -5984,7 +5984,7 @@
       </c>
       <c r="P74" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q74" s="4" t="n"/>
@@ -6061,7 +6061,7 @@
       </c>
       <c r="P75" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q75" s="4" t="n"/>
@@ -6138,7 +6138,7 @@
       </c>
       <c r="P76" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q76" s="4" t="n"/>
@@ -6215,7 +6215,7 @@
       </c>
       <c r="P77" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q77" s="4" t="n"/>
@@ -6294,7 +6294,7 @@
       </c>
       <c r="P78" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q78" s="4" t="n"/>
@@ -6371,7 +6371,7 @@
       </c>
       <c r="P79" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q79" s="4" t="n"/>
@@ -6448,7 +6448,7 @@
       </c>
       <c r="P80" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q80" s="4" t="n"/>
@@ -6525,7 +6525,7 @@
       </c>
       <c r="P81" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q81" s="4" t="n"/>
@@ -6602,7 +6602,7 @@
       </c>
       <c r="P82" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q82" s="4" t="n"/>
@@ -6681,7 +6681,7 @@
       </c>
       <c r="P83" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q83" s="4" t="n"/>
@@ -6758,7 +6758,7 @@
       </c>
       <c r="P84" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q84" s="4" t="n"/>
@@ -6835,7 +6835,7 @@
       </c>
       <c r="P85" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q85" s="4" t="n"/>
@@ -6912,7 +6912,7 @@
       </c>
       <c r="P86" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q86" s="4" t="n"/>
@@ -6989,7 +6989,7 @@
       </c>
       <c r="P87" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q87" s="4" t="n"/>
@@ -7068,7 +7068,7 @@
       </c>
       <c r="P88" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q88" s="4" t="n"/>
@@ -7147,7 +7147,7 @@
       </c>
       <c r="P89" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q89" s="4" t="n"/>
@@ -7226,7 +7226,7 @@
       </c>
       <c r="P90" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q90" s="4" t="n"/>
@@ -7305,7 +7305,7 @@
       </c>
       <c r="P91" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q91" s="4" t="n"/>
@@ -7384,7 +7384,7 @@
       </c>
       <c r="P92" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q92" s="4" t="n"/>
@@ -7463,7 +7463,7 @@
       </c>
       <c r="P93" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q93" s="4" t="n"/>
@@ -7542,7 +7542,7 @@
       </c>
       <c r="P94" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q94" s="4" t="n"/>
@@ -7621,7 +7621,7 @@
       </c>
       <c r="P95" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q95" s="4" t="n"/>
@@ -7700,7 +7700,7 @@
       </c>
       <c r="P96" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q96" s="4" t="n"/>
@@ -7779,7 +7779,7 @@
       </c>
       <c r="P97" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q97" s="4" t="n"/>
@@ -7858,7 +7858,7 @@
       </c>
       <c r="P98" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q98" s="4" t="n"/>
@@ -7937,7 +7937,7 @@
       </c>
       <c r="P99" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q99" s="4" t="n"/>
@@ -8016,7 +8016,7 @@
       </c>
       <c r="P100" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q100" s="4" t="n"/>
@@ -8095,7 +8095,7 @@
       </c>
       <c r="P101" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q101" s="4" t="n"/>
@@ -8174,7 +8174,7 @@
       </c>
       <c r="P102" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q102" s="4" t="n"/>
@@ -8253,7 +8253,7 @@
       </c>
       <c r="P103" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q103" s="4" t="n"/>
@@ -8332,7 +8332,7 @@
       </c>
       <c r="P104" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q104" s="4" t="n"/>
@@ -8411,7 +8411,7 @@
       </c>
       <c r="P105" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q105" s="4" t="n"/>
@@ -8490,7 +8490,7 @@
       </c>
       <c r="P106" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q106" s="4" t="n"/>
@@ -8569,7 +8569,7 @@
       </c>
       <c r="P107" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q107" s="4" t="n"/>
@@ -8648,7 +8648,7 @@
       </c>
       <c r="P108" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q108" s="4" t="n"/>
@@ -8727,7 +8727,7 @@
       </c>
       <c r="P109" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q109" s="4" t="n"/>
@@ -8806,7 +8806,7 @@
       </c>
       <c r="P110" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q110" s="4" t="n"/>
@@ -8885,7 +8885,7 @@
       </c>
       <c r="P111" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q111" s="4" t="n"/>
@@ -8964,7 +8964,7 @@
       </c>
       <c r="P112" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q112" s="4" t="n"/>
@@ -9043,7 +9043,7 @@
       </c>
       <c r="P113" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q113" s="4" t="n"/>
@@ -9122,7 +9122,7 @@
       </c>
       <c r="P114" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q114" s="4" t="n"/>
@@ -9201,7 +9201,7 @@
       </c>
       <c r="P115" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q115" s="4" t="n"/>
@@ -9280,7 +9280,7 @@
       </c>
       <c r="P116" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q116" s="4" t="n"/>
@@ -9359,7 +9359,7 @@
       </c>
       <c r="P117" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q117" s="4" t="n"/>
@@ -9438,7 +9438,7 @@
       </c>
       <c r="P118" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q118" s="4" t="n"/>
@@ -9517,7 +9517,7 @@
       </c>
       <c r="P119" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q119" s="4" t="n"/>
@@ -9596,7 +9596,7 @@
       </c>
       <c r="P120" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q120" s="4" t="n"/>
@@ -9675,7 +9675,7 @@
       </c>
       <c r="P121" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q121" s="4" t="n"/>
@@ -9754,7 +9754,7 @@
       </c>
       <c r="P122" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q122" s="4" t="n"/>
@@ -9833,7 +9833,7 @@
       </c>
       <c r="P123" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q123" s="4" t="n"/>
@@ -9912,7 +9912,7 @@
       </c>
       <c r="P124" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q124" s="4" t="n"/>
@@ -9991,7 +9991,7 @@
       </c>
       <c r="P125" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q125" s="4" t="n"/>
@@ -10070,7 +10070,7 @@
       </c>
       <c r="P126" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q126" s="4" t="n"/>
@@ -10149,7 +10149,7 @@
       </c>
       <c r="P127" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q127" s="4" t="n"/>
@@ -10228,7 +10228,7 @@
       </c>
       <c r="P128" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q128" s="4" t="n"/>
@@ -10307,7 +10307,7 @@
       </c>
       <c r="P129" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q129" s="4" t="n"/>
@@ -10386,7 +10386,7 @@
       </c>
       <c r="P130" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q130" s="4" t="n"/>
@@ -10465,7 +10465,7 @@
       </c>
       <c r="P131" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q131" s="4" t="n"/>
@@ -10544,7 +10544,7 @@
       </c>
       <c r="P132" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q132" s="4" t="n"/>
@@ -10623,7 +10623,7 @@
       </c>
       <c r="P133" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q133" s="4" t="n"/>
@@ -10702,7 +10702,7 @@
       </c>
       <c r="P134" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q134" s="4" t="n"/>
@@ -10781,7 +10781,7 @@
       </c>
       <c r="P135" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q135" s="4" t="n"/>
@@ -10860,7 +10860,7 @@
       </c>
       <c r="P136" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q136" s="4" t="n"/>
@@ -10939,7 +10939,7 @@
       </c>
       <c r="P137" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q137" s="4" t="n"/>
@@ -11016,7 +11016,7 @@
       </c>
       <c r="P138" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q138" s="4" t="n"/>
@@ -11093,7 +11093,7 @@
       </c>
       <c r="P139" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q139" s="4" t="n"/>
@@ -11170,7 +11170,7 @@
       </c>
       <c r="P140" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q140" s="4" t="n"/>
@@ -11247,7 +11247,7 @@
       </c>
       <c r="P141" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q141" s="4" t="n"/>
@@ -11324,7 +11324,7 @@
       </c>
       <c r="P142" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q142" s="4" t="n"/>
@@ -11401,7 +11401,7 @@
       </c>
       <c r="P143" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q143" s="4" t="n"/>
@@ -11478,7 +11478,7 @@
       </c>
       <c r="P144" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q144" s="4" t="n"/>
@@ -11555,7 +11555,7 @@
       </c>
       <c r="P145" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q145" s="4" t="n"/>
@@ -11632,7 +11632,7 @@
       </c>
       <c r="P146" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q146" s="4" t="n"/>
@@ -11709,7 +11709,7 @@
       </c>
       <c r="P147" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q147" s="4" t="n"/>
@@ -11786,7 +11786,7 @@
       </c>
       <c r="P148" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q148" s="4" t="n"/>
@@ -11863,7 +11863,7 @@
       </c>
       <c r="P149" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q149" s="4" t="n"/>
@@ -11940,7 +11940,7 @@
       </c>
       <c r="P150" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q150" s="4" t="n"/>
@@ -12017,7 +12017,7 @@
       </c>
       <c r="P151" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q151" s="4" t="n"/>
@@ -12094,7 +12094,7 @@
       </c>
       <c r="P152" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q152" s="4" t="n"/>
@@ -12171,7 +12171,7 @@
       </c>
       <c r="P153" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q153" s="4" t="n"/>
@@ -12248,7 +12248,7 @@
       </c>
       <c r="P154" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q154" s="4" t="n"/>
@@ -12325,7 +12325,7 @@
       </c>
       <c r="P155" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q155" s="4" t="n"/>
@@ -12402,7 +12402,7 @@
       </c>
       <c r="P156" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q156" s="4" t="n"/>
@@ -12479,7 +12479,7 @@
       </c>
       <c r="P157" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q157" s="4" t="n"/>
@@ -12556,7 +12556,7 @@
       </c>
       <c r="P158" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q158" s="4" t="n"/>
@@ -12633,7 +12633,7 @@
       </c>
       <c r="P159" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q159" s="4" t="n"/>
@@ -12710,7 +12710,7 @@
       </c>
       <c r="P160" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q160" s="4" t="n"/>
@@ -12787,7 +12787,7 @@
       </c>
       <c r="P161" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q161" s="4" t="n"/>
@@ -12864,7 +12864,7 @@
       </c>
       <c r="P162" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q162" s="4" t="n"/>
@@ -12941,7 +12941,7 @@
       </c>
       <c r="P163" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q163" s="4" t="n"/>
@@ -13018,7 +13018,7 @@
       </c>
       <c r="P164" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q164" s="4" t="n"/>
@@ -13095,7 +13095,7 @@
       </c>
       <c r="P165" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q165" s="4" t="n"/>
@@ -13172,7 +13172,7 @@
       </c>
       <c r="P166" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q166" s="4" t="n"/>
@@ -13249,7 +13249,7 @@
       </c>
       <c r="P167" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q167" s="4" t="n"/>
@@ -13326,7 +13326,7 @@
       </c>
       <c r="P168" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q168" s="4" t="n"/>
@@ -13403,7 +13403,7 @@
       </c>
       <c r="P169" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q169" s="4" t="n"/>
@@ -13480,7 +13480,7 @@
       </c>
       <c r="P170" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q170" s="4" t="n"/>
@@ -13557,7 +13557,7 @@
       </c>
       <c r="P171" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q171" s="4" t="n"/>
@@ -13634,7 +13634,7 @@
       </c>
       <c r="P172" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q172" s="4" t="n"/>
@@ -13711,7 +13711,7 @@
       </c>
       <c r="P173" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q173" s="4" t="n"/>
@@ -13788,7 +13788,7 @@
       </c>
       <c r="P174" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q174" s="4" t="n"/>
@@ -13865,7 +13865,7 @@
       </c>
       <c r="P175" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q175" s="4" t="n"/>
@@ -13942,7 +13942,7 @@
       </c>
       <c r="P176" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q176" s="4" t="n"/>
@@ -14019,7 +14019,7 @@
       </c>
       <c r="P177" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q177" s="4" t="n"/>
@@ -14096,7 +14096,7 @@
       </c>
       <c r="P178" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q178" s="4" t="n"/>
@@ -14175,7 +14175,7 @@
       </c>
       <c r="P179" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q179" s="4" t="n"/>
@@ -14254,7 +14254,7 @@
       </c>
       <c r="P180" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q180" s="4" t="n"/>
@@ -14333,7 +14333,7 @@
       </c>
       <c r="P181" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q181" s="4" t="n"/>
@@ -14412,7 +14412,7 @@
       </c>
       <c r="P182" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q182" s="4" t="n"/>
@@ -14491,7 +14491,7 @@
       </c>
       <c r="P183" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q183" s="4" t="n"/>
@@ -14570,7 +14570,7 @@
       </c>
       <c r="P184" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q184" s="4" t="n"/>
@@ -14649,7 +14649,7 @@
       </c>
       <c r="P185" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q185" s="4" t="n"/>
@@ -14728,7 +14728,7 @@
       </c>
       <c r="P186" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q186" s="4" t="n"/>
@@ -14807,7 +14807,7 @@
       </c>
       <c r="P187" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q187" s="4" t="n"/>
@@ -14886,7 +14886,7 @@
       </c>
       <c r="P188" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q188" s="4" t="n"/>
@@ -14965,7 +14965,7 @@
       </c>
       <c r="P189" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q189" s="4" t="n"/>
@@ -15044,7 +15044,7 @@
       </c>
       <c r="P190" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q190" s="4" t="n"/>
@@ -15123,7 +15123,7 @@
       </c>
       <c r="P191" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q191" s="4" t="n"/>
@@ -15202,7 +15202,7 @@
       </c>
       <c r="P192" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q192" s="4" t="n"/>
@@ -15281,7 +15281,7 @@
       </c>
       <c r="P193" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q193" s="4" t="n"/>
@@ -15360,7 +15360,7 @@
       </c>
       <c r="P194" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q194" s="4" t="n"/>
@@ -15439,7 +15439,7 @@
       </c>
       <c r="P195" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q195" s="4" t="n"/>
@@ -15518,7 +15518,7 @@
       </c>
       <c r="P196" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q196" s="4" t="n"/>
@@ -15597,7 +15597,7 @@
       </c>
       <c r="P197" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q197" s="4" t="n"/>
@@ -15676,7 +15676,7 @@
       </c>
       <c r="P198" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q198" s="4" t="n"/>
@@ -15755,7 +15755,7 @@
       </c>
       <c r="P199" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q199" s="4" t="n"/>
@@ -15834,7 +15834,7 @@
       </c>
       <c r="P200" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q200" s="4" t="n"/>
@@ -15913,7 +15913,7 @@
       </c>
       <c r="P201" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q201" s="4" t="n"/>
@@ -15992,7 +15992,7 @@
       </c>
       <c r="P202" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q202" s="4" t="n"/>
@@ -16071,7 +16071,7 @@
       </c>
       <c r="P203" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q203" s="4" t="n"/>
@@ -16148,7 +16148,7 @@
       </c>
       <c r="P204" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q204" s="4" t="n"/>
@@ -16225,7 +16225,7 @@
       </c>
       <c r="P205" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q205" s="4" t="n"/>
@@ -16302,7 +16302,7 @@
       </c>
       <c r="P206" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q206" s="4" t="n"/>
@@ -16379,7 +16379,7 @@
       </c>
       <c r="P207" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q207" s="4" t="n"/>
@@ -16456,7 +16456,7 @@
       </c>
       <c r="P208" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q208" s="4" t="n"/>
@@ -16533,7 +16533,7 @@
       </c>
       <c r="P209" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q209" s="4" t="n"/>
@@ -16610,7 +16610,7 @@
       </c>
       <c r="P210" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q210" s="4" t="n"/>
@@ -16687,7 +16687,7 @@
       </c>
       <c r="P211" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q211" s="4" t="n"/>
@@ -16764,7 +16764,7 @@
       </c>
       <c r="P212" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q212" s="4" t="n"/>
@@ -16841,7 +16841,7 @@
       </c>
       <c r="P213" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q213" s="4" t="n"/>
@@ -16918,7 +16918,7 @@
       </c>
       <c r="P214" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q214" s="4" t="n"/>
@@ -16995,7 +16995,7 @@
       </c>
       <c r="P215" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q215" s="4" t="n"/>
@@ -17072,7 +17072,7 @@
       </c>
       <c r="P216" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q216" s="4" t="n"/>
@@ -17149,7 +17149,7 @@
       </c>
       <c r="P217" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q217" s="4" t="n"/>
@@ -17226,7 +17226,7 @@
       </c>
       <c r="P218" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q218" s="4" t="n"/>
@@ -17303,7 +17303,7 @@
       </c>
       <c r="P219" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q219" s="4" t="n"/>
@@ -17380,7 +17380,7 @@
       </c>
       <c r="P220" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q220" s="4" t="n"/>
@@ -17457,7 +17457,7 @@
       </c>
       <c r="P221" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q221" s="4" t="n"/>
@@ -17534,7 +17534,7 @@
       </c>
       <c r="P222" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q222" s="4" t="n"/>
@@ -17611,7 +17611,7 @@
       </c>
       <c r="P223" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q223" s="4" t="n"/>
@@ -17688,7 +17688,7 @@
       </c>
       <c r="P224" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q224" s="4" t="n"/>
@@ -17765,7 +17765,7 @@
       </c>
       <c r="P225" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q225" s="4" t="n"/>
@@ -17842,7 +17842,7 @@
       </c>
       <c r="P226" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q226" s="4" t="n"/>
@@ -17919,7 +17919,7 @@
       </c>
       <c r="P227" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q227" s="4" t="n"/>
@@ -17996,7 +17996,7 @@
       </c>
       <c r="P228" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q228" s="4" t="n"/>
@@ -18073,7 +18073,7 @@
       </c>
       <c r="P229" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q229" s="4" t="n"/>
@@ -18150,7 +18150,7 @@
       </c>
       <c r="P230" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q230" s="4" t="n"/>
@@ -18227,7 +18227,7 @@
       </c>
       <c r="P231" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q231" s="4" t="n"/>
@@ -18304,7 +18304,7 @@
       </c>
       <c r="P232" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q232" s="4" t="n"/>
@@ -18381,7 +18381,7 @@
       </c>
       <c r="P233" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q233" s="4" t="n"/>
@@ -18458,7 +18458,7 @@
       </c>
       <c r="P234" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q234" s="4" t="n"/>
@@ -18537,7 +18537,7 @@
       </c>
       <c r="P235" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q235" s="4" t="n"/>
@@ -18614,7 +18614,7 @@
       </c>
       <c r="P236" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q236" s="4" t="n"/>
@@ -18693,7 +18693,7 @@
       </c>
       <c r="P237" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q237" s="4" t="n"/>
@@ -18772,7 +18772,7 @@
       </c>
       <c r="P238" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q238" s="4" t="n"/>
@@ -18851,7 +18851,7 @@
       </c>
       <c r="P239" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q239" s="4" t="n"/>
@@ -18930,7 +18930,7 @@
       </c>
       <c r="P240" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q240" s="4" t="n"/>
@@ -19009,7 +19009,7 @@
       </c>
       <c r="P241" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q241" s="4" t="n"/>
@@ -19088,7 +19088,7 @@
       </c>
       <c r="P242" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q242" s="4" t="n"/>
@@ -19167,7 +19167,7 @@
       </c>
       <c r="P243" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q243" s="4" t="n"/>
@@ -19246,7 +19246,7 @@
       </c>
       <c r="P244" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q244" s="4" t="n"/>
@@ -19325,7 +19325,7 @@
       </c>
       <c r="P245" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q245" s="4" t="n"/>
@@ -19404,7 +19404,7 @@
       </c>
       <c r="P246" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q246" s="4" t="n"/>
@@ -19483,7 +19483,7 @@
       </c>
       <c r="P247" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q247" s="4" t="n"/>
@@ -19562,7 +19562,7 @@
       </c>
       <c r="P248" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q248" s="4" t="n"/>
@@ -19641,7 +19641,7 @@
       </c>
       <c r="P249" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q249" s="4" t="n"/>
@@ -19720,7 +19720,7 @@
       </c>
       <c r="P250" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q250" s="4" t="n"/>
@@ -19799,7 +19799,7 @@
       </c>
       <c r="P251" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q251" s="4" t="n"/>
@@ -19878,7 +19878,7 @@
       </c>
       <c r="P252" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q252" s="4" t="n"/>
@@ -19957,7 +19957,7 @@
       </c>
       <c r="P253" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q253" s="4" t="n"/>
@@ -20036,7 +20036,7 @@
       </c>
       <c r="P254" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q254" s="4" t="n"/>
@@ -20115,7 +20115,7 @@
       </c>
       <c r="P255" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q255" s="4" t="n"/>
@@ -20194,7 +20194,7 @@
       </c>
       <c r="P256" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q256" s="4" t="n"/>
@@ -20273,7 +20273,7 @@
       </c>
       <c r="P257" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q257" s="4" t="n"/>
@@ -20352,7 +20352,7 @@
       </c>
       <c r="P258" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q258" s="4" t="n"/>
@@ -20431,7 +20431,7 @@
       </c>
       <c r="P259" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q259" s="4" t="n"/>
@@ -20510,7 +20510,7 @@
       </c>
       <c r="P260" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q260" s="4" t="n"/>
@@ -20589,7 +20589,7 @@
       </c>
       <c r="P261" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q261" s="4" t="n"/>
@@ -20666,7 +20666,7 @@
       </c>
       <c r="P262" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q262" s="4" t="n"/>
@@ -20743,7 +20743,7 @@
       </c>
       <c r="P263" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q263" s="4" t="n"/>
@@ -20822,7 +20822,7 @@
       </c>
       <c r="P264" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q264" s="4" t="n"/>
@@ -20901,7 +20901,7 @@
       </c>
       <c r="P265" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q265" s="4" t="n"/>
@@ -20980,7 +20980,7 @@
       </c>
       <c r="P266" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q266" s="4" t="n"/>
@@ -21059,7 +21059,7 @@
       </c>
       <c r="P267" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q267" s="4" t="n"/>
@@ -21138,7 +21138,7 @@
       </c>
       <c r="P268" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q268" s="4" t="n"/>
@@ -21217,7 +21217,7 @@
       </c>
       <c r="P269" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q269" s="4" t="n"/>
@@ -21294,7 +21294,7 @@
       </c>
       <c r="P270" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q270" s="4" t="n"/>
@@ -21379,7 +21379,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
     </row>

--- a/assets/data/world-bank/excel/ove_banco_mundial_venezuela_infraestructura_y_digitalizacion.xlsx
+++ b/assets/data/world-bank/excel/ove_banco_mundial_venezuela_infraestructura_y_digitalizacion.xlsx
@@ -715,7 +715,7 @@
       </c>
       <c r="P7" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q7" s="4" t="n"/>
@@ -792,7 +792,7 @@
       </c>
       <c r="P8" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q8" s="4" t="n"/>
@@ -869,7 +869,7 @@
       </c>
       <c r="P9" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q9" s="4" t="n"/>
@@ -946,7 +946,7 @@
       </c>
       <c r="P10" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q10" s="4" t="n"/>
@@ -1023,7 +1023,7 @@
       </c>
       <c r="P11" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q11" s="4" t="n"/>
@@ -1100,7 +1100,7 @@
       </c>
       <c r="P12" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q12" s="4" t="n"/>
@@ -1177,7 +1177,7 @@
       </c>
       <c r="P13" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q13" s="4" t="n"/>
@@ -1254,7 +1254,7 @@
       </c>
       <c r="P14" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q14" s="4" t="n"/>
@@ -1331,7 +1331,7 @@
       </c>
       <c r="P15" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q15" s="4" t="n"/>
@@ -1408,7 +1408,7 @@
       </c>
       <c r="P16" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q16" s="4" t="n"/>
@@ -1487,7 +1487,7 @@
       </c>
       <c r="P17" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q17" s="4" t="n"/>
@@ -1566,7 +1566,7 @@
       </c>
       <c r="P18" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q18" s="4" t="n"/>
@@ -1645,7 +1645,7 @@
       </c>
       <c r="P19" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q19" s="4" t="n"/>
@@ -1724,7 +1724,7 @@
       </c>
       <c r="P20" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q20" s="4" t="n"/>
@@ -1803,7 +1803,7 @@
       </c>
       <c r="P21" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q21" s="4" t="n"/>
@@ -1882,7 +1882,7 @@
       </c>
       <c r="P22" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q22" s="4" t="n"/>
@@ -1961,7 +1961,7 @@
       </c>
       <c r="P23" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q23" s="4" t="n"/>
@@ -2040,7 +2040,7 @@
       </c>
       <c r="P24" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q24" s="4" t="n"/>
@@ -2119,7 +2119,7 @@
       </c>
       <c r="P25" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q25" s="4" t="n"/>
@@ -2198,7 +2198,7 @@
       </c>
       <c r="P26" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q26" s="4" t="n"/>
@@ -2277,7 +2277,7 @@
       </c>
       <c r="P27" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q27" s="4" t="n"/>
@@ -2356,7 +2356,7 @@
       </c>
       <c r="P28" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q28" s="4" t="n"/>
@@ -2435,7 +2435,7 @@
       </c>
       <c r="P29" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q29" s="4" t="n"/>
@@ -2514,7 +2514,7 @@
       </c>
       <c r="P30" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q30" s="4" t="n"/>
@@ -2593,7 +2593,7 @@
       </c>
       <c r="P31" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q31" s="4" t="n"/>
@@ -2672,7 +2672,7 @@
       </c>
       <c r="P32" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q32" s="4" t="n"/>
@@ -2751,7 +2751,7 @@
       </c>
       <c r="P33" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q33" s="4" t="n"/>
@@ -2830,7 +2830,7 @@
       </c>
       <c r="P34" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q34" s="4" t="n"/>
@@ -2909,7 +2909,7 @@
       </c>
       <c r="P35" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q35" s="4" t="n"/>
@@ -2988,7 +2988,7 @@
       </c>
       <c r="P36" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q36" s="4" t="n"/>
@@ -3067,7 +3067,7 @@
       </c>
       <c r="P37" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q37" s="4" t="n"/>
@@ -3146,7 +3146,7 @@
       </c>
       <c r="P38" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q38" s="4" t="n"/>
@@ -3225,7 +3225,7 @@
       </c>
       <c r="P39" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q39" s="4" t="n"/>
@@ -3304,7 +3304,7 @@
       </c>
       <c r="P40" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q40" s="4" t="n"/>
@@ -3383,7 +3383,7 @@
       </c>
       <c r="P41" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q41" s="4" t="n"/>
@@ -3462,7 +3462,7 @@
       </c>
       <c r="P42" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q42" s="4" t="n"/>
@@ -3541,7 +3541,7 @@
       </c>
       <c r="P43" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q43" s="4" t="n"/>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="P44" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q44" s="4" t="n"/>
@@ -3699,7 +3699,7 @@
       </c>
       <c r="P45" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q45" s="4" t="n"/>
@@ -3778,7 +3778,7 @@
       </c>
       <c r="P46" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q46" s="4" t="n"/>
@@ -3857,7 +3857,7 @@
       </c>
       <c r="P47" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q47" s="4" t="n"/>
@@ -3936,7 +3936,7 @@
       </c>
       <c r="P48" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q48" s="4" t="n"/>
@@ -4015,7 +4015,7 @@
       </c>
       <c r="P49" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q49" s="4" t="n"/>
@@ -4094,7 +4094,7 @@
       </c>
       <c r="P50" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q50" s="4" t="n"/>
@@ -4173,7 +4173,7 @@
       </c>
       <c r="P51" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q51" s="4" t="n"/>
@@ -4252,7 +4252,7 @@
       </c>
       <c r="P52" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q52" s="4" t="n"/>
@@ -4331,7 +4331,7 @@
       </c>
       <c r="P53" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q53" s="4" t="n"/>
@@ -4410,7 +4410,7 @@
       </c>
       <c r="P54" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q54" s="4" t="n"/>
@@ -4489,7 +4489,7 @@
       </c>
       <c r="P55" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q55" s="4" t="n"/>
@@ -4568,7 +4568,7 @@
       </c>
       <c r="P56" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q56" s="4" t="n"/>
@@ -4647,7 +4647,7 @@
       </c>
       <c r="P57" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q57" s="4" t="n"/>
@@ -4726,7 +4726,7 @@
       </c>
       <c r="P58" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q58" s="4" t="n"/>
@@ -4805,7 +4805,7 @@
       </c>
       <c r="P59" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q59" s="4" t="n"/>
@@ -4884,7 +4884,7 @@
       </c>
       <c r="P60" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q60" s="4" t="n"/>
@@ -4963,7 +4963,7 @@
       </c>
       <c r="P61" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q61" s="4" t="n"/>
@@ -5042,7 +5042,7 @@
       </c>
       <c r="P62" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q62" s="4" t="n"/>
@@ -5121,7 +5121,7 @@
       </c>
       <c r="P63" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q63" s="4" t="n"/>
@@ -5200,7 +5200,7 @@
       </c>
       <c r="P64" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q64" s="4" t="n"/>
@@ -5279,7 +5279,7 @@
       </c>
       <c r="P65" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q65" s="4" t="n"/>
@@ -5358,7 +5358,7 @@
       </c>
       <c r="P66" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q66" s="4" t="n"/>
@@ -5437,7 +5437,7 @@
       </c>
       <c r="P67" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q67" s="4" t="n"/>
@@ -5516,7 +5516,7 @@
       </c>
       <c r="P68" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q68" s="4" t="n"/>
@@ -5595,7 +5595,7 @@
       </c>
       <c r="P69" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q69" s="4" t="n"/>
@@ -5674,7 +5674,7 @@
       </c>
       <c r="P70" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q70" s="4" t="n"/>
@@ -5751,7 +5751,7 @@
       </c>
       <c r="P71" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q71" s="4" t="n"/>
@@ -5828,7 +5828,7 @@
       </c>
       <c r="P72" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q72" s="4" t="n"/>
@@ -5907,7 +5907,7 @@
       </c>
       <c r="P73" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q73" s="4" t="n"/>
@@ -5984,7 +5984,7 @@
       </c>
       <c r="P74" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q74" s="4" t="n"/>
@@ -6061,7 +6061,7 @@
       </c>
       <c r="P75" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q75" s="4" t="n"/>
@@ -6138,7 +6138,7 @@
       </c>
       <c r="P76" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q76" s="4" t="n"/>
@@ -6215,7 +6215,7 @@
       </c>
       <c r="P77" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q77" s="4" t="n"/>
@@ -6294,7 +6294,7 @@
       </c>
       <c r="P78" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q78" s="4" t="n"/>
@@ -6371,7 +6371,7 @@
       </c>
       <c r="P79" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q79" s="4" t="n"/>
@@ -6448,7 +6448,7 @@
       </c>
       <c r="P80" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q80" s="4" t="n"/>
@@ -6525,7 +6525,7 @@
       </c>
       <c r="P81" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q81" s="4" t="n"/>
@@ -6602,7 +6602,7 @@
       </c>
       <c r="P82" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q82" s="4" t="n"/>
@@ -6681,7 +6681,7 @@
       </c>
       <c r="P83" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q83" s="4" t="n"/>
@@ -6758,7 +6758,7 @@
       </c>
       <c r="P84" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q84" s="4" t="n"/>
@@ -6835,7 +6835,7 @@
       </c>
       <c r="P85" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q85" s="4" t="n"/>
@@ -6912,7 +6912,7 @@
       </c>
       <c r="P86" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q86" s="4" t="n"/>
@@ -6989,7 +6989,7 @@
       </c>
       <c r="P87" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q87" s="4" t="n"/>
@@ -7068,7 +7068,7 @@
       </c>
       <c r="P88" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q88" s="4" t="n"/>
@@ -7147,7 +7147,7 @@
       </c>
       <c r="P89" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q89" s="4" t="n"/>
@@ -7226,7 +7226,7 @@
       </c>
       <c r="P90" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q90" s="4" t="n"/>
@@ -7305,7 +7305,7 @@
       </c>
       <c r="P91" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q91" s="4" t="n"/>
@@ -7384,7 +7384,7 @@
       </c>
       <c r="P92" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q92" s="4" t="n"/>
@@ -7463,7 +7463,7 @@
       </c>
       <c r="P93" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q93" s="4" t="n"/>
@@ -7542,7 +7542,7 @@
       </c>
       <c r="P94" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q94" s="4" t="n"/>
@@ -7621,7 +7621,7 @@
       </c>
       <c r="P95" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q95" s="4" t="n"/>
@@ -7700,7 +7700,7 @@
       </c>
       <c r="P96" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q96" s="4" t="n"/>
@@ -7779,7 +7779,7 @@
       </c>
       <c r="P97" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q97" s="4" t="n"/>
@@ -7858,7 +7858,7 @@
       </c>
       <c r="P98" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q98" s="4" t="n"/>
@@ -7937,7 +7937,7 @@
       </c>
       <c r="P99" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q99" s="4" t="n"/>
@@ -8016,7 +8016,7 @@
       </c>
       <c r="P100" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q100" s="4" t="n"/>
@@ -8095,7 +8095,7 @@
       </c>
       <c r="P101" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q101" s="4" t="n"/>
@@ -8174,7 +8174,7 @@
       </c>
       <c r="P102" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q102" s="4" t="n"/>
@@ -8253,7 +8253,7 @@
       </c>
       <c r="P103" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q103" s="4" t="n"/>
@@ -8332,7 +8332,7 @@
       </c>
       <c r="P104" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q104" s="4" t="n"/>
@@ -8411,7 +8411,7 @@
       </c>
       <c r="P105" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q105" s="4" t="n"/>
@@ -8490,7 +8490,7 @@
       </c>
       <c r="P106" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q106" s="4" t="n"/>
@@ -8569,7 +8569,7 @@
       </c>
       <c r="P107" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q107" s="4" t="n"/>
@@ -8648,7 +8648,7 @@
       </c>
       <c r="P108" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q108" s="4" t="n"/>
@@ -8727,7 +8727,7 @@
       </c>
       <c r="P109" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q109" s="4" t="n"/>
@@ -8806,7 +8806,7 @@
       </c>
       <c r="P110" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q110" s="4" t="n"/>
@@ -8885,7 +8885,7 @@
       </c>
       <c r="P111" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q111" s="4" t="n"/>
@@ -8964,7 +8964,7 @@
       </c>
       <c r="P112" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q112" s="4" t="n"/>
@@ -9043,7 +9043,7 @@
       </c>
       <c r="P113" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q113" s="4" t="n"/>
@@ -9122,7 +9122,7 @@
       </c>
       <c r="P114" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q114" s="4" t="n"/>
@@ -9201,7 +9201,7 @@
       </c>
       <c r="P115" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q115" s="4" t="n"/>
@@ -9280,7 +9280,7 @@
       </c>
       <c r="P116" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q116" s="4" t="n"/>
@@ -9359,7 +9359,7 @@
       </c>
       <c r="P117" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q117" s="4" t="n"/>
@@ -9438,7 +9438,7 @@
       </c>
       <c r="P118" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q118" s="4" t="n"/>
@@ -9517,7 +9517,7 @@
       </c>
       <c r="P119" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q119" s="4" t="n"/>
@@ -9596,7 +9596,7 @@
       </c>
       <c r="P120" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q120" s="4" t="n"/>
@@ -9675,7 +9675,7 @@
       </c>
       <c r="P121" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q121" s="4" t="n"/>
@@ -9754,7 +9754,7 @@
       </c>
       <c r="P122" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q122" s="4" t="n"/>
@@ -9833,7 +9833,7 @@
       </c>
       <c r="P123" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q123" s="4" t="n"/>
@@ -9912,7 +9912,7 @@
       </c>
       <c r="P124" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q124" s="4" t="n"/>
@@ -9991,7 +9991,7 @@
       </c>
       <c r="P125" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q125" s="4" t="n"/>
@@ -10070,7 +10070,7 @@
       </c>
       <c r="P126" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q126" s="4" t="n"/>
@@ -10149,7 +10149,7 @@
       </c>
       <c r="P127" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q127" s="4" t="n"/>
@@ -10228,7 +10228,7 @@
       </c>
       <c r="P128" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q128" s="4" t="n"/>
@@ -10307,7 +10307,7 @@
       </c>
       <c r="P129" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q129" s="4" t="n"/>
@@ -10386,7 +10386,7 @@
       </c>
       <c r="P130" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q130" s="4" t="n"/>
@@ -10465,7 +10465,7 @@
       </c>
       <c r="P131" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q131" s="4" t="n"/>
@@ -10544,7 +10544,7 @@
       </c>
       <c r="P132" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q132" s="4" t="n"/>
@@ -10623,7 +10623,7 @@
       </c>
       <c r="P133" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q133" s="4" t="n"/>
@@ -10702,7 +10702,7 @@
       </c>
       <c r="P134" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q134" s="4" t="n"/>
@@ -10781,7 +10781,7 @@
       </c>
       <c r="P135" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q135" s="4" t="n"/>
@@ -10860,7 +10860,7 @@
       </c>
       <c r="P136" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q136" s="4" t="n"/>
@@ -10939,7 +10939,7 @@
       </c>
       <c r="P137" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q137" s="4" t="n"/>
@@ -11016,7 +11016,7 @@
       </c>
       <c r="P138" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q138" s="4" t="n"/>
@@ -11093,7 +11093,7 @@
       </c>
       <c r="P139" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q139" s="4" t="n"/>
@@ -11170,7 +11170,7 @@
       </c>
       <c r="P140" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q140" s="4" t="n"/>
@@ -11247,7 +11247,7 @@
       </c>
       <c r="P141" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q141" s="4" t="n"/>
@@ -11324,7 +11324,7 @@
       </c>
       <c r="P142" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q142" s="4" t="n"/>
@@ -11401,7 +11401,7 @@
       </c>
       <c r="P143" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q143" s="4" t="n"/>
@@ -11478,7 +11478,7 @@
       </c>
       <c r="P144" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q144" s="4" t="n"/>
@@ -11555,7 +11555,7 @@
       </c>
       <c r="P145" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q145" s="4" t="n"/>
@@ -11632,7 +11632,7 @@
       </c>
       <c r="P146" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q146" s="4" t="n"/>
@@ -11709,7 +11709,7 @@
       </c>
       <c r="P147" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q147" s="4" t="n"/>
@@ -11786,7 +11786,7 @@
       </c>
       <c r="P148" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q148" s="4" t="n"/>
@@ -11863,7 +11863,7 @@
       </c>
       <c r="P149" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q149" s="4" t="n"/>
@@ -11940,7 +11940,7 @@
       </c>
       <c r="P150" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q150" s="4" t="n"/>
@@ -12017,7 +12017,7 @@
       </c>
       <c r="P151" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q151" s="4" t="n"/>
@@ -12094,7 +12094,7 @@
       </c>
       <c r="P152" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q152" s="4" t="n"/>
@@ -12171,7 +12171,7 @@
       </c>
       <c r="P153" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q153" s="4" t="n"/>
@@ -12248,7 +12248,7 @@
       </c>
       <c r="P154" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q154" s="4" t="n"/>
@@ -12325,7 +12325,7 @@
       </c>
       <c r="P155" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q155" s="4" t="n"/>
@@ -12402,7 +12402,7 @@
       </c>
       <c r="P156" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q156" s="4" t="n"/>
@@ -12479,7 +12479,7 @@
       </c>
       <c r="P157" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q157" s="4" t="n"/>
@@ -12556,7 +12556,7 @@
       </c>
       <c r="P158" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q158" s="4" t="n"/>
@@ -12633,7 +12633,7 @@
       </c>
       <c r="P159" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q159" s="4" t="n"/>
@@ -12710,7 +12710,7 @@
       </c>
       <c r="P160" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q160" s="4" t="n"/>
@@ -12787,7 +12787,7 @@
       </c>
       <c r="P161" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q161" s="4" t="n"/>
@@ -12864,7 +12864,7 @@
       </c>
       <c r="P162" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q162" s="4" t="n"/>
@@ -12941,7 +12941,7 @@
       </c>
       <c r="P163" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q163" s="4" t="n"/>
@@ -13018,7 +13018,7 @@
       </c>
       <c r="P164" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q164" s="4" t="n"/>
@@ -13095,7 +13095,7 @@
       </c>
       <c r="P165" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q165" s="4" t="n"/>
@@ -13172,7 +13172,7 @@
       </c>
       <c r="P166" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q166" s="4" t="n"/>
@@ -13249,7 +13249,7 @@
       </c>
       <c r="P167" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q167" s="4" t="n"/>
@@ -13326,7 +13326,7 @@
       </c>
       <c r="P168" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q168" s="4" t="n"/>
@@ -13403,7 +13403,7 @@
       </c>
       <c r="P169" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q169" s="4" t="n"/>
@@ -13480,7 +13480,7 @@
       </c>
       <c r="P170" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q170" s="4" t="n"/>
@@ -13557,7 +13557,7 @@
       </c>
       <c r="P171" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q171" s="4" t="n"/>
@@ -13634,7 +13634,7 @@
       </c>
       <c r="P172" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q172" s="4" t="n"/>
@@ -13711,7 +13711,7 @@
       </c>
       <c r="P173" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q173" s="4" t="n"/>
@@ -13788,7 +13788,7 @@
       </c>
       <c r="P174" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q174" s="4" t="n"/>
@@ -13865,7 +13865,7 @@
       </c>
       <c r="P175" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q175" s="4" t="n"/>
@@ -13942,7 +13942,7 @@
       </c>
       <c r="P176" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q176" s="4" t="n"/>
@@ -14019,7 +14019,7 @@
       </c>
       <c r="P177" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q177" s="4" t="n"/>
@@ -14096,7 +14096,7 @@
       </c>
       <c r="P178" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q178" s="4" t="n"/>
@@ -14175,7 +14175,7 @@
       </c>
       <c r="P179" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q179" s="4" t="n"/>
@@ -14254,7 +14254,7 @@
       </c>
       <c r="P180" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q180" s="4" t="n"/>
@@ -14333,7 +14333,7 @@
       </c>
       <c r="P181" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q181" s="4" t="n"/>
@@ -14412,7 +14412,7 @@
       </c>
       <c r="P182" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q182" s="4" t="n"/>
@@ -14491,7 +14491,7 @@
       </c>
       <c r="P183" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q183" s="4" t="n"/>
@@ -14570,7 +14570,7 @@
       </c>
       <c r="P184" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q184" s="4" t="n"/>
@@ -14649,7 +14649,7 @@
       </c>
       <c r="P185" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q185" s="4" t="n"/>
@@ -14728,7 +14728,7 @@
       </c>
       <c r="P186" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q186" s="4" t="n"/>
@@ -14807,7 +14807,7 @@
       </c>
       <c r="P187" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q187" s="4" t="n"/>
@@ -14886,7 +14886,7 @@
       </c>
       <c r="P188" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q188" s="4" t="n"/>
@@ -14965,7 +14965,7 @@
       </c>
       <c r="P189" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q189" s="4" t="n"/>
@@ -15044,7 +15044,7 @@
       </c>
       <c r="P190" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q190" s="4" t="n"/>
@@ -15123,7 +15123,7 @@
       </c>
       <c r="P191" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q191" s="4" t="n"/>
@@ -15202,7 +15202,7 @@
       </c>
       <c r="P192" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q192" s="4" t="n"/>
@@ -15281,7 +15281,7 @@
       </c>
       <c r="P193" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q193" s="4" t="n"/>
@@ -15360,7 +15360,7 @@
       </c>
       <c r="P194" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q194" s="4" t="n"/>
@@ -15439,7 +15439,7 @@
       </c>
       <c r="P195" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q195" s="4" t="n"/>
@@ -15518,7 +15518,7 @@
       </c>
       <c r="P196" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q196" s="4" t="n"/>
@@ -15597,7 +15597,7 @@
       </c>
       <c r="P197" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q197" s="4" t="n"/>
@@ -15676,7 +15676,7 @@
       </c>
       <c r="P198" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q198" s="4" t="n"/>
@@ -15755,7 +15755,7 @@
       </c>
       <c r="P199" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q199" s="4" t="n"/>
@@ -15834,7 +15834,7 @@
       </c>
       <c r="P200" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q200" s="4" t="n"/>
@@ -15913,7 +15913,7 @@
       </c>
       <c r="P201" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q201" s="4" t="n"/>
@@ -15992,7 +15992,7 @@
       </c>
       <c r="P202" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q202" s="4" t="n"/>
@@ -16071,7 +16071,7 @@
       </c>
       <c r="P203" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q203" s="4" t="n"/>
@@ -16148,7 +16148,7 @@
       </c>
       <c r="P204" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q204" s="4" t="n"/>
@@ -16225,7 +16225,7 @@
       </c>
       <c r="P205" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q205" s="4" t="n"/>
@@ -16302,7 +16302,7 @@
       </c>
       <c r="P206" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q206" s="4" t="n"/>
@@ -16379,7 +16379,7 @@
       </c>
       <c r="P207" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q207" s="4" t="n"/>
@@ -16456,7 +16456,7 @@
       </c>
       <c r="P208" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q208" s="4" t="n"/>
@@ -16533,7 +16533,7 @@
       </c>
       <c r="P209" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q209" s="4" t="n"/>
@@ -16610,7 +16610,7 @@
       </c>
       <c r="P210" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q210" s="4" t="n"/>
@@ -16687,7 +16687,7 @@
       </c>
       <c r="P211" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q211" s="4" t="n"/>
@@ -16764,7 +16764,7 @@
       </c>
       <c r="P212" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q212" s="4" t="n"/>
@@ -16841,7 +16841,7 @@
       </c>
       <c r="P213" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q213" s="4" t="n"/>
@@ -16918,7 +16918,7 @@
       </c>
       <c r="P214" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q214" s="4" t="n"/>
@@ -16995,7 +16995,7 @@
       </c>
       <c r="P215" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q215" s="4" t="n"/>
@@ -17072,7 +17072,7 @@
       </c>
       <c r="P216" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q216" s="4" t="n"/>
@@ -17149,7 +17149,7 @@
       </c>
       <c r="P217" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q217" s="4" t="n"/>
@@ -17226,7 +17226,7 @@
       </c>
       <c r="P218" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q218" s="4" t="n"/>
@@ -17303,7 +17303,7 @@
       </c>
       <c r="P219" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q219" s="4" t="n"/>
@@ -17380,7 +17380,7 @@
       </c>
       <c r="P220" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q220" s="4" t="n"/>
@@ -17457,7 +17457,7 @@
       </c>
       <c r="P221" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q221" s="4" t="n"/>
@@ -17534,7 +17534,7 @@
       </c>
       <c r="P222" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q222" s="4" t="n"/>
@@ -17611,7 +17611,7 @@
       </c>
       <c r="P223" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q223" s="4" t="n"/>
@@ -17688,7 +17688,7 @@
       </c>
       <c r="P224" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q224" s="4" t="n"/>
@@ -17765,7 +17765,7 @@
       </c>
       <c r="P225" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q225" s="4" t="n"/>
@@ -17842,7 +17842,7 @@
       </c>
       <c r="P226" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q226" s="4" t="n"/>
@@ -17919,7 +17919,7 @@
       </c>
       <c r="P227" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q227" s="4" t="n"/>
@@ -17996,7 +17996,7 @@
       </c>
       <c r="P228" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q228" s="4" t="n"/>
@@ -18073,7 +18073,7 @@
       </c>
       <c r="P229" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q229" s="4" t="n"/>
@@ -18150,7 +18150,7 @@
       </c>
       <c r="P230" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q230" s="4" t="n"/>
@@ -18227,7 +18227,7 @@
       </c>
       <c r="P231" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q231" s="4" t="n"/>
@@ -18304,7 +18304,7 @@
       </c>
       <c r="P232" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q232" s="4" t="n"/>
@@ -18381,7 +18381,7 @@
       </c>
       <c r="P233" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q233" s="4" t="n"/>
@@ -18458,7 +18458,7 @@
       </c>
       <c r="P234" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q234" s="4" t="n"/>
@@ -18537,7 +18537,7 @@
       </c>
       <c r="P235" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q235" s="4" t="n"/>
@@ -18614,7 +18614,7 @@
       </c>
       <c r="P236" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q236" s="4" t="n"/>
@@ -18693,7 +18693,7 @@
       </c>
       <c r="P237" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q237" s="4" t="n"/>
@@ -18772,7 +18772,7 @@
       </c>
       <c r="P238" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q238" s="4" t="n"/>
@@ -18851,7 +18851,7 @@
       </c>
       <c r="P239" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q239" s="4" t="n"/>
@@ -18930,7 +18930,7 @@
       </c>
       <c r="P240" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q240" s="4" t="n"/>
@@ -19009,7 +19009,7 @@
       </c>
       <c r="P241" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q241" s="4" t="n"/>
@@ -19088,7 +19088,7 @@
       </c>
       <c r="P242" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q242" s="4" t="n"/>
@@ -19167,7 +19167,7 @@
       </c>
       <c r="P243" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q243" s="4" t="n"/>
@@ -19246,7 +19246,7 @@
       </c>
       <c r="P244" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q244" s="4" t="n"/>
@@ -19325,7 +19325,7 @@
       </c>
       <c r="P245" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q245" s="4" t="n"/>
@@ -19404,7 +19404,7 @@
       </c>
       <c r="P246" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q246" s="4" t="n"/>
@@ -19483,7 +19483,7 @@
       </c>
       <c r="P247" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q247" s="4" t="n"/>
@@ -19562,7 +19562,7 @@
       </c>
       <c r="P248" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q248" s="4" t="n"/>
@@ -19641,7 +19641,7 @@
       </c>
       <c r="P249" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q249" s="4" t="n"/>
@@ -19720,7 +19720,7 @@
       </c>
       <c r="P250" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q250" s="4" t="n"/>
@@ -19799,7 +19799,7 @@
       </c>
       <c r="P251" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q251" s="4" t="n"/>
@@ -19878,7 +19878,7 @@
       </c>
       <c r="P252" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q252" s="4" t="n"/>
@@ -19957,7 +19957,7 @@
       </c>
       <c r="P253" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q253" s="4" t="n"/>
@@ -20036,7 +20036,7 @@
       </c>
       <c r="P254" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q254" s="4" t="n"/>
@@ -20115,7 +20115,7 @@
       </c>
       <c r="P255" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q255" s="4" t="n"/>
@@ -20194,7 +20194,7 @@
       </c>
       <c r="P256" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q256" s="4" t="n"/>
@@ -20273,7 +20273,7 @@
       </c>
       <c r="P257" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q257" s="4" t="n"/>
@@ -20352,7 +20352,7 @@
       </c>
       <c r="P258" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q258" s="4" t="n"/>
@@ -20431,7 +20431,7 @@
       </c>
       <c r="P259" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q259" s="4" t="n"/>
@@ -20510,7 +20510,7 @@
       </c>
       <c r="P260" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q260" s="4" t="n"/>
@@ -20589,7 +20589,7 @@
       </c>
       <c r="P261" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q261" s="4" t="n"/>
@@ -20666,7 +20666,7 @@
       </c>
       <c r="P262" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q262" s="4" t="n"/>
@@ -20743,7 +20743,7 @@
       </c>
       <c r="P263" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q263" s="4" t="n"/>
@@ -20822,7 +20822,7 @@
       </c>
       <c r="P264" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q264" s="4" t="n"/>
@@ -20901,7 +20901,7 @@
       </c>
       <c r="P265" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q265" s="4" t="n"/>
@@ -20980,7 +20980,7 @@
       </c>
       <c r="P266" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q266" s="4" t="n"/>
@@ -21059,7 +21059,7 @@
       </c>
       <c r="P267" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q267" s="4" t="n"/>
@@ -21138,7 +21138,7 @@
       </c>
       <c r="P268" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q268" s="4" t="n"/>
@@ -21217,7 +21217,7 @@
       </c>
       <c r="P269" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q269" s="4" t="n"/>
@@ -21294,7 +21294,7 @@
       </c>
       <c r="P270" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q270" s="4" t="n"/>
@@ -21379,7 +21379,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
     </row>

--- a/assets/data/world-bank/excel/ove_banco_mundial_venezuela_infraestructura_y_digitalizacion.xlsx
+++ b/assets/data/world-bank/excel/ove_banco_mundial_venezuela_infraestructura_y_digitalizacion.xlsx
@@ -715,7 +715,7 @@
       </c>
       <c r="P7" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q7" s="4" t="n"/>
@@ -792,7 +792,7 @@
       </c>
       <c r="P8" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q8" s="4" t="n"/>
@@ -869,7 +869,7 @@
       </c>
       <c r="P9" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q9" s="4" t="n"/>
@@ -946,7 +946,7 @@
       </c>
       <c r="P10" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q10" s="4" t="n"/>
@@ -1023,7 +1023,7 @@
       </c>
       <c r="P11" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q11" s="4" t="n"/>
@@ -1100,7 +1100,7 @@
       </c>
       <c r="P12" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q12" s="4" t="n"/>
@@ -1177,7 +1177,7 @@
       </c>
       <c r="P13" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q13" s="4" t="n"/>
@@ -1254,7 +1254,7 @@
       </c>
       <c r="P14" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q14" s="4" t="n"/>
@@ -1331,7 +1331,7 @@
       </c>
       <c r="P15" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q15" s="4" t="n"/>
@@ -1408,7 +1408,7 @@
       </c>
       <c r="P16" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q16" s="4" t="n"/>
@@ -1487,7 +1487,7 @@
       </c>
       <c r="P17" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q17" s="4" t="n"/>
@@ -1566,7 +1566,7 @@
       </c>
       <c r="P18" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q18" s="4" t="n"/>
@@ -1645,7 +1645,7 @@
       </c>
       <c r="P19" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q19" s="4" t="n"/>
@@ -1724,7 +1724,7 @@
       </c>
       <c r="P20" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q20" s="4" t="n"/>
@@ -1803,7 +1803,7 @@
       </c>
       <c r="P21" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q21" s="4" t="n"/>
@@ -1882,7 +1882,7 @@
       </c>
       <c r="P22" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q22" s="4" t="n"/>
@@ -1961,7 +1961,7 @@
       </c>
       <c r="P23" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q23" s="4" t="n"/>
@@ -2040,7 +2040,7 @@
       </c>
       <c r="P24" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q24" s="4" t="n"/>
@@ -2119,7 +2119,7 @@
       </c>
       <c r="P25" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q25" s="4" t="n"/>
@@ -2198,7 +2198,7 @@
       </c>
       <c r="P26" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q26" s="4" t="n"/>
@@ -2277,7 +2277,7 @@
       </c>
       <c r="P27" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q27" s="4" t="n"/>
@@ -2356,7 +2356,7 @@
       </c>
       <c r="P28" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q28" s="4" t="n"/>
@@ -2435,7 +2435,7 @@
       </c>
       <c r="P29" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q29" s="4" t="n"/>
@@ -2514,7 +2514,7 @@
       </c>
       <c r="P30" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q30" s="4" t="n"/>
@@ -2593,7 +2593,7 @@
       </c>
       <c r="P31" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q31" s="4" t="n"/>
@@ -2672,7 +2672,7 @@
       </c>
       <c r="P32" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q32" s="4" t="n"/>
@@ -2751,7 +2751,7 @@
       </c>
       <c r="P33" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q33" s="4" t="n"/>
@@ -2830,7 +2830,7 @@
       </c>
       <c r="P34" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q34" s="4" t="n"/>
@@ -2909,7 +2909,7 @@
       </c>
       <c r="P35" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q35" s="4" t="n"/>
@@ -2988,7 +2988,7 @@
       </c>
       <c r="P36" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q36" s="4" t="n"/>
@@ -3067,7 +3067,7 @@
       </c>
       <c r="P37" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q37" s="4" t="n"/>
@@ -3146,7 +3146,7 @@
       </c>
       <c r="P38" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q38" s="4" t="n"/>
@@ -3225,7 +3225,7 @@
       </c>
       <c r="P39" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q39" s="4" t="n"/>
@@ -3304,7 +3304,7 @@
       </c>
       <c r="P40" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q40" s="4" t="n"/>
@@ -3383,7 +3383,7 @@
       </c>
       <c r="P41" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q41" s="4" t="n"/>
@@ -3462,7 +3462,7 @@
       </c>
       <c r="P42" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q42" s="4" t="n"/>
@@ -3541,7 +3541,7 @@
       </c>
       <c r="P43" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q43" s="4" t="n"/>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="P44" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q44" s="4" t="n"/>
@@ -3699,7 +3699,7 @@
       </c>
       <c r="P45" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q45" s="4" t="n"/>
@@ -3778,7 +3778,7 @@
       </c>
       <c r="P46" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q46" s="4" t="n"/>
@@ -3857,7 +3857,7 @@
       </c>
       <c r="P47" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q47" s="4" t="n"/>
@@ -3936,7 +3936,7 @@
       </c>
       <c r="P48" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q48" s="4" t="n"/>
@@ -4015,7 +4015,7 @@
       </c>
       <c r="P49" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q49" s="4" t="n"/>
@@ -4094,7 +4094,7 @@
       </c>
       <c r="P50" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q50" s="4" t="n"/>
@@ -4173,7 +4173,7 @@
       </c>
       <c r="P51" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q51" s="4" t="n"/>
@@ -4252,7 +4252,7 @@
       </c>
       <c r="P52" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q52" s="4" t="n"/>
@@ -4331,7 +4331,7 @@
       </c>
       <c r="P53" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q53" s="4" t="n"/>
@@ -4410,7 +4410,7 @@
       </c>
       <c r="P54" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q54" s="4" t="n"/>
@@ -4489,7 +4489,7 @@
       </c>
       <c r="P55" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q55" s="4" t="n"/>
@@ -4568,7 +4568,7 @@
       </c>
       <c r="P56" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q56" s="4" t="n"/>
@@ -4647,7 +4647,7 @@
       </c>
       <c r="P57" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q57" s="4" t="n"/>
@@ -4726,7 +4726,7 @@
       </c>
       <c r="P58" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q58" s="4" t="n"/>
@@ -4805,7 +4805,7 @@
       </c>
       <c r="P59" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q59" s="4" t="n"/>
@@ -4884,7 +4884,7 @@
       </c>
       <c r="P60" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q60" s="4" t="n"/>
@@ -4963,7 +4963,7 @@
       </c>
       <c r="P61" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q61" s="4" t="n"/>
@@ -5042,7 +5042,7 @@
       </c>
       <c r="P62" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q62" s="4" t="n"/>
@@ -5121,7 +5121,7 @@
       </c>
       <c r="P63" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q63" s="4" t="n"/>
@@ -5200,7 +5200,7 @@
       </c>
       <c r="P64" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q64" s="4" t="n"/>
@@ -5279,7 +5279,7 @@
       </c>
       <c r="P65" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q65" s="4" t="n"/>
@@ -5358,7 +5358,7 @@
       </c>
       <c r="P66" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q66" s="4" t="n"/>
@@ -5437,7 +5437,7 @@
       </c>
       <c r="P67" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q67" s="4" t="n"/>
@@ -5516,7 +5516,7 @@
       </c>
       <c r="P68" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q68" s="4" t="n"/>
@@ -5595,7 +5595,7 @@
       </c>
       <c r="P69" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q69" s="4" t="n"/>
@@ -5674,7 +5674,7 @@
       </c>
       <c r="P70" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q70" s="4" t="n"/>
@@ -5751,7 +5751,7 @@
       </c>
       <c r="P71" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q71" s="4" t="n"/>
@@ -5828,7 +5828,7 @@
       </c>
       <c r="P72" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q72" s="4" t="n"/>
@@ -5907,7 +5907,7 @@
       </c>
       <c r="P73" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q73" s="4" t="n"/>
@@ -5984,7 +5984,7 @@
       </c>
       <c r="P74" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q74" s="4" t="n"/>
@@ -6061,7 +6061,7 @@
       </c>
       <c r="P75" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q75" s="4" t="n"/>
@@ -6138,7 +6138,7 @@
       </c>
       <c r="P76" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q76" s="4" t="n"/>
@@ -6215,7 +6215,7 @@
       </c>
       <c r="P77" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q77" s="4" t="n"/>
@@ -6294,7 +6294,7 @@
       </c>
       <c r="P78" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q78" s="4" t="n"/>
@@ -6371,7 +6371,7 @@
       </c>
       <c r="P79" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q79" s="4" t="n"/>
@@ -6448,7 +6448,7 @@
       </c>
       <c r="P80" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q80" s="4" t="n"/>
@@ -6525,7 +6525,7 @@
       </c>
       <c r="P81" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q81" s="4" t="n"/>
@@ -6602,7 +6602,7 @@
       </c>
       <c r="P82" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q82" s="4" t="n"/>
@@ -6681,7 +6681,7 @@
       </c>
       <c r="P83" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q83" s="4" t="n"/>
@@ -6758,7 +6758,7 @@
       </c>
       <c r="P84" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q84" s="4" t="n"/>
@@ -6835,7 +6835,7 @@
       </c>
       <c r="P85" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q85" s="4" t="n"/>
@@ -6912,7 +6912,7 @@
       </c>
       <c r="P86" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q86" s="4" t="n"/>
@@ -6989,7 +6989,7 @@
       </c>
       <c r="P87" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q87" s="4" t="n"/>
@@ -7068,7 +7068,7 @@
       </c>
       <c r="P88" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q88" s="4" t="n"/>
@@ -7147,7 +7147,7 @@
       </c>
       <c r="P89" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q89" s="4" t="n"/>
@@ -7226,7 +7226,7 @@
       </c>
       <c r="P90" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q90" s="4" t="n"/>
@@ -7305,7 +7305,7 @@
       </c>
       <c r="P91" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q91" s="4" t="n"/>
@@ -7384,7 +7384,7 @@
       </c>
       <c r="P92" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q92" s="4" t="n"/>
@@ -7463,7 +7463,7 @@
       </c>
       <c r="P93" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q93" s="4" t="n"/>
@@ -7542,7 +7542,7 @@
       </c>
       <c r="P94" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q94" s="4" t="n"/>
@@ -7621,7 +7621,7 @@
       </c>
       <c r="P95" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q95" s="4" t="n"/>
@@ -7700,7 +7700,7 @@
       </c>
       <c r="P96" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q96" s="4" t="n"/>
@@ -7779,7 +7779,7 @@
       </c>
       <c r="P97" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q97" s="4" t="n"/>
@@ -7858,7 +7858,7 @@
       </c>
       <c r="P98" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q98" s="4" t="n"/>
@@ -7937,7 +7937,7 @@
       </c>
       <c r="P99" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q99" s="4" t="n"/>
@@ -8016,7 +8016,7 @@
       </c>
       <c r="P100" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q100" s="4" t="n"/>
@@ -8095,7 +8095,7 @@
       </c>
       <c r="P101" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q101" s="4" t="n"/>
@@ -8174,7 +8174,7 @@
       </c>
       <c r="P102" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q102" s="4" t="n"/>
@@ -8253,7 +8253,7 @@
       </c>
       <c r="P103" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q103" s="4" t="n"/>
@@ -8332,7 +8332,7 @@
       </c>
       <c r="P104" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q104" s="4" t="n"/>
@@ -8411,7 +8411,7 @@
       </c>
       <c r="P105" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q105" s="4" t="n"/>
@@ -8490,7 +8490,7 @@
       </c>
       <c r="P106" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q106" s="4" t="n"/>
@@ -8569,7 +8569,7 @@
       </c>
       <c r="P107" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q107" s="4" t="n"/>
@@ -8648,7 +8648,7 @@
       </c>
       <c r="P108" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q108" s="4" t="n"/>
@@ -8727,7 +8727,7 @@
       </c>
       <c r="P109" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q109" s="4" t="n"/>
@@ -8806,7 +8806,7 @@
       </c>
       <c r="P110" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q110" s="4" t="n"/>
@@ -8885,7 +8885,7 @@
       </c>
       <c r="P111" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q111" s="4" t="n"/>
@@ -8964,7 +8964,7 @@
       </c>
       <c r="P112" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q112" s="4" t="n"/>
@@ -9043,7 +9043,7 @@
       </c>
       <c r="P113" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q113" s="4" t="n"/>
@@ -9122,7 +9122,7 @@
       </c>
       <c r="P114" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q114" s="4" t="n"/>
@@ -9201,7 +9201,7 @@
       </c>
       <c r="P115" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q115" s="4" t="n"/>
@@ -9280,7 +9280,7 @@
       </c>
       <c r="P116" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q116" s="4" t="n"/>
@@ -9359,7 +9359,7 @@
       </c>
       <c r="P117" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q117" s="4" t="n"/>
@@ -9438,7 +9438,7 @@
       </c>
       <c r="P118" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q118" s="4" t="n"/>
@@ -9517,7 +9517,7 @@
       </c>
       <c r="P119" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q119" s="4" t="n"/>
@@ -9596,7 +9596,7 @@
       </c>
       <c r="P120" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q120" s="4" t="n"/>
@@ -9675,7 +9675,7 @@
       </c>
       <c r="P121" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q121" s="4" t="n"/>
@@ -9754,7 +9754,7 @@
       </c>
       <c r="P122" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q122" s="4" t="n"/>
@@ -9833,7 +9833,7 @@
       </c>
       <c r="P123" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q123" s="4" t="n"/>
@@ -9912,7 +9912,7 @@
       </c>
       <c r="P124" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q124" s="4" t="n"/>
@@ -9991,7 +9991,7 @@
       </c>
       <c r="P125" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q125" s="4" t="n"/>
@@ -10070,7 +10070,7 @@
       </c>
       <c r="P126" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q126" s="4" t="n"/>
@@ -10149,7 +10149,7 @@
       </c>
       <c r="P127" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q127" s="4" t="n"/>
@@ -10228,7 +10228,7 @@
       </c>
       <c r="P128" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q128" s="4" t="n"/>
@@ -10307,7 +10307,7 @@
       </c>
       <c r="P129" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q129" s="4" t="n"/>
@@ -10386,7 +10386,7 @@
       </c>
       <c r="P130" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q130" s="4" t="n"/>
@@ -10465,7 +10465,7 @@
       </c>
       <c r="P131" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q131" s="4" t="n"/>
@@ -10544,7 +10544,7 @@
       </c>
       <c r="P132" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q132" s="4" t="n"/>
@@ -10623,7 +10623,7 @@
       </c>
       <c r="P133" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q133" s="4" t="n"/>
@@ -10702,7 +10702,7 @@
       </c>
       <c r="P134" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q134" s="4" t="n"/>
@@ -10781,7 +10781,7 @@
       </c>
       <c r="P135" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q135" s="4" t="n"/>
@@ -10860,7 +10860,7 @@
       </c>
       <c r="P136" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q136" s="4" t="n"/>
@@ -10939,7 +10939,7 @@
       </c>
       <c r="P137" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q137" s="4" t="n"/>
@@ -11016,7 +11016,7 @@
       </c>
       <c r="P138" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q138" s="4" t="n"/>
@@ -11093,7 +11093,7 @@
       </c>
       <c r="P139" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q139" s="4" t="n"/>
@@ -11170,7 +11170,7 @@
       </c>
       <c r="P140" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q140" s="4" t="n"/>
@@ -11247,7 +11247,7 @@
       </c>
       <c r="P141" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q141" s="4" t="n"/>
@@ -11324,7 +11324,7 @@
       </c>
       <c r="P142" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q142" s="4" t="n"/>
@@ -11401,7 +11401,7 @@
       </c>
       <c r="P143" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q143" s="4" t="n"/>
@@ -11478,7 +11478,7 @@
       </c>
       <c r="P144" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q144" s="4" t="n"/>
@@ -11555,7 +11555,7 @@
       </c>
       <c r="P145" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q145" s="4" t="n"/>
@@ -11632,7 +11632,7 @@
       </c>
       <c r="P146" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q146" s="4" t="n"/>
@@ -11709,7 +11709,7 @@
       </c>
       <c r="P147" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q147" s="4" t="n"/>
@@ -11786,7 +11786,7 @@
       </c>
       <c r="P148" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q148" s="4" t="n"/>
@@ -11863,7 +11863,7 @@
       </c>
       <c r="P149" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q149" s="4" t="n"/>
@@ -11940,7 +11940,7 @@
       </c>
       <c r="P150" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q150" s="4" t="n"/>
@@ -12017,7 +12017,7 @@
       </c>
       <c r="P151" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q151" s="4" t="n"/>
@@ -12094,7 +12094,7 @@
       </c>
       <c r="P152" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q152" s="4" t="n"/>
@@ -12171,7 +12171,7 @@
       </c>
       <c r="P153" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q153" s="4" t="n"/>
@@ -12248,7 +12248,7 @@
       </c>
       <c r="P154" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q154" s="4" t="n"/>
@@ -12325,7 +12325,7 @@
       </c>
       <c r="P155" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q155" s="4" t="n"/>
@@ -12402,7 +12402,7 @@
       </c>
       <c r="P156" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q156" s="4" t="n"/>
@@ -12479,7 +12479,7 @@
       </c>
       <c r="P157" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q157" s="4" t="n"/>
@@ -12556,7 +12556,7 @@
       </c>
       <c r="P158" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q158" s="4" t="n"/>
@@ -12633,7 +12633,7 @@
       </c>
       <c r="P159" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q159" s="4" t="n"/>
@@ -12710,7 +12710,7 @@
       </c>
       <c r="P160" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q160" s="4" t="n"/>
@@ -12787,7 +12787,7 @@
       </c>
       <c r="P161" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q161" s="4" t="n"/>
@@ -12864,7 +12864,7 @@
       </c>
       <c r="P162" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q162" s="4" t="n"/>
@@ -12941,7 +12941,7 @@
       </c>
       <c r="P163" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q163" s="4" t="n"/>
@@ -13018,7 +13018,7 @@
       </c>
       <c r="P164" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q164" s="4" t="n"/>
@@ -13095,7 +13095,7 @@
       </c>
       <c r="P165" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q165" s="4" t="n"/>
@@ -13172,7 +13172,7 @@
       </c>
       <c r="P166" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q166" s="4" t="n"/>
@@ -13249,7 +13249,7 @@
       </c>
       <c r="P167" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q167" s="4" t="n"/>
@@ -13326,7 +13326,7 @@
       </c>
       <c r="P168" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q168" s="4" t="n"/>
@@ -13403,7 +13403,7 @@
       </c>
       <c r="P169" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q169" s="4" t="n"/>
@@ -13480,7 +13480,7 @@
       </c>
       <c r="P170" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q170" s="4" t="n"/>
@@ -13557,7 +13557,7 @@
       </c>
       <c r="P171" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q171" s="4" t="n"/>
@@ -13634,7 +13634,7 @@
       </c>
       <c r="P172" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q172" s="4" t="n"/>
@@ -13711,7 +13711,7 @@
       </c>
       <c r="P173" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q173" s="4" t="n"/>
@@ -13788,7 +13788,7 @@
       </c>
       <c r="P174" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q174" s="4" t="n"/>
@@ -13865,7 +13865,7 @@
       </c>
       <c r="P175" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q175" s="4" t="n"/>
@@ -13942,7 +13942,7 @@
       </c>
       <c r="P176" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q176" s="4" t="n"/>
@@ -14019,7 +14019,7 @@
       </c>
       <c r="P177" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q177" s="4" t="n"/>
@@ -14096,7 +14096,7 @@
       </c>
       <c r="P178" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q178" s="4" t="n"/>
@@ -14175,7 +14175,7 @@
       </c>
       <c r="P179" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q179" s="4" t="n"/>
@@ -14254,7 +14254,7 @@
       </c>
       <c r="P180" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q180" s="4" t="n"/>
@@ -14333,7 +14333,7 @@
       </c>
       <c r="P181" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q181" s="4" t="n"/>
@@ -14412,7 +14412,7 @@
       </c>
       <c r="P182" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q182" s="4" t="n"/>
@@ -14491,7 +14491,7 @@
       </c>
       <c r="P183" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q183" s="4" t="n"/>
@@ -14570,7 +14570,7 @@
       </c>
       <c r="P184" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q184" s="4" t="n"/>
@@ -14649,7 +14649,7 @@
       </c>
       <c r="P185" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q185" s="4" t="n"/>
@@ -14728,7 +14728,7 @@
       </c>
       <c r="P186" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q186" s="4" t="n"/>
@@ -14807,7 +14807,7 @@
       </c>
       <c r="P187" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q187" s="4" t="n"/>
@@ -14886,7 +14886,7 @@
       </c>
       <c r="P188" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q188" s="4" t="n"/>
@@ -14965,7 +14965,7 @@
       </c>
       <c r="P189" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q189" s="4" t="n"/>
@@ -15044,7 +15044,7 @@
       </c>
       <c r="P190" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q190" s="4" t="n"/>
@@ -15123,7 +15123,7 @@
       </c>
       <c r="P191" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q191" s="4" t="n"/>
@@ -15202,7 +15202,7 @@
       </c>
       <c r="P192" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q192" s="4" t="n"/>
@@ -15281,7 +15281,7 @@
       </c>
       <c r="P193" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q193" s="4" t="n"/>
@@ -15360,7 +15360,7 @@
       </c>
       <c r="P194" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q194" s="4" t="n"/>
@@ -15439,7 +15439,7 @@
       </c>
       <c r="P195" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q195" s="4" t="n"/>
@@ -15518,7 +15518,7 @@
       </c>
       <c r="P196" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q196" s="4" t="n"/>
@@ -15597,7 +15597,7 @@
       </c>
       <c r="P197" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q197" s="4" t="n"/>
@@ -15676,7 +15676,7 @@
       </c>
       <c r="P198" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q198" s="4" t="n"/>
@@ -15755,7 +15755,7 @@
       </c>
       <c r="P199" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q199" s="4" t="n"/>
@@ -15834,7 +15834,7 @@
       </c>
       <c r="P200" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q200" s="4" t="n"/>
@@ -15913,7 +15913,7 @@
       </c>
       <c r="P201" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q201" s="4" t="n"/>
@@ -15992,7 +15992,7 @@
       </c>
       <c r="P202" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q202" s="4" t="n"/>
@@ -16071,7 +16071,7 @@
       </c>
       <c r="P203" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q203" s="4" t="n"/>
@@ -16148,7 +16148,7 @@
       </c>
       <c r="P204" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q204" s="4" t="n"/>
@@ -16225,7 +16225,7 @@
       </c>
       <c r="P205" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q205" s="4" t="n"/>
@@ -16302,7 +16302,7 @@
       </c>
       <c r="P206" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q206" s="4" t="n"/>
@@ -16379,7 +16379,7 @@
       </c>
       <c r="P207" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q207" s="4" t="n"/>
@@ -16456,7 +16456,7 @@
       </c>
       <c r="P208" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q208" s="4" t="n"/>
@@ -16533,7 +16533,7 @@
       </c>
       <c r="P209" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q209" s="4" t="n"/>
@@ -16610,7 +16610,7 @@
       </c>
       <c r="P210" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q210" s="4" t="n"/>
@@ -16687,7 +16687,7 @@
       </c>
       <c r="P211" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q211" s="4" t="n"/>
@@ -16764,7 +16764,7 @@
       </c>
       <c r="P212" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q212" s="4" t="n"/>
@@ -16841,7 +16841,7 @@
       </c>
       <c r="P213" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q213" s="4" t="n"/>
@@ -16918,7 +16918,7 @@
       </c>
       <c r="P214" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q214" s="4" t="n"/>
@@ -16995,7 +16995,7 @@
       </c>
       <c r="P215" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q215" s="4" t="n"/>
@@ -17072,7 +17072,7 @@
       </c>
       <c r="P216" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q216" s="4" t="n"/>
@@ -17149,7 +17149,7 @@
       </c>
       <c r="P217" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q217" s="4" t="n"/>
@@ -17226,7 +17226,7 @@
       </c>
       <c r="P218" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q218" s="4" t="n"/>
@@ -17303,7 +17303,7 @@
       </c>
       <c r="P219" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q219" s="4" t="n"/>
@@ -17380,7 +17380,7 @@
       </c>
       <c r="P220" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q220" s="4" t="n"/>
@@ -17457,7 +17457,7 @@
       </c>
       <c r="P221" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q221" s="4" t="n"/>
@@ -17534,7 +17534,7 @@
       </c>
       <c r="P222" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q222" s="4" t="n"/>
@@ -17611,7 +17611,7 @@
       </c>
       <c r="P223" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q223" s="4" t="n"/>
@@ -17688,7 +17688,7 @@
       </c>
       <c r="P224" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q224" s="4" t="n"/>
@@ -17765,7 +17765,7 @@
       </c>
       <c r="P225" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q225" s="4" t="n"/>
@@ -17842,7 +17842,7 @@
       </c>
       <c r="P226" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q226" s="4" t="n"/>
@@ -17919,7 +17919,7 @@
       </c>
       <c r="P227" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q227" s="4" t="n"/>
@@ -17996,7 +17996,7 @@
       </c>
       <c r="P228" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q228" s="4" t="n"/>
@@ -18073,7 +18073,7 @@
       </c>
       <c r="P229" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q229" s="4" t="n"/>
@@ -18150,7 +18150,7 @@
       </c>
       <c r="P230" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q230" s="4" t="n"/>
@@ -18227,7 +18227,7 @@
       </c>
       <c r="P231" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q231" s="4" t="n"/>
@@ -18304,7 +18304,7 @@
       </c>
       <c r="P232" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q232" s="4" t="n"/>
@@ -18381,7 +18381,7 @@
       </c>
       <c r="P233" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q233" s="4" t="n"/>
@@ -18458,7 +18458,7 @@
       </c>
       <c r="P234" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q234" s="4" t="n"/>
@@ -18537,7 +18537,7 @@
       </c>
       <c r="P235" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q235" s="4" t="n"/>
@@ -18614,7 +18614,7 @@
       </c>
       <c r="P236" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q236" s="4" t="n"/>
@@ -18693,7 +18693,7 @@
       </c>
       <c r="P237" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q237" s="4" t="n"/>
@@ -18772,7 +18772,7 @@
       </c>
       <c r="P238" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q238" s="4" t="n"/>
@@ -18851,7 +18851,7 @@
       </c>
       <c r="P239" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q239" s="4" t="n"/>
@@ -18930,7 +18930,7 @@
       </c>
       <c r="P240" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q240" s="4" t="n"/>
@@ -19009,7 +19009,7 @@
       </c>
       <c r="P241" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q241" s="4" t="n"/>
@@ -19088,7 +19088,7 @@
       </c>
       <c r="P242" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q242" s="4" t="n"/>
@@ -19167,7 +19167,7 @@
       </c>
       <c r="P243" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q243" s="4" t="n"/>
@@ -19246,7 +19246,7 @@
       </c>
       <c r="P244" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q244" s="4" t="n"/>
@@ -19325,7 +19325,7 @@
       </c>
       <c r="P245" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q245" s="4" t="n"/>
@@ -19404,7 +19404,7 @@
       </c>
       <c r="P246" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q246" s="4" t="n"/>
@@ -19483,7 +19483,7 @@
       </c>
       <c r="P247" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q247" s="4" t="n"/>
@@ -19562,7 +19562,7 @@
       </c>
       <c r="P248" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q248" s="4" t="n"/>
@@ -19641,7 +19641,7 @@
       </c>
       <c r="P249" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q249" s="4" t="n"/>
@@ -19720,7 +19720,7 @@
       </c>
       <c r="P250" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q250" s="4" t="n"/>
@@ -19799,7 +19799,7 @@
       </c>
       <c r="P251" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q251" s="4" t="n"/>
@@ -19878,7 +19878,7 @@
       </c>
       <c r="P252" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q252" s="4" t="n"/>
@@ -19957,7 +19957,7 @@
       </c>
       <c r="P253" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q253" s="4" t="n"/>
@@ -20036,7 +20036,7 @@
       </c>
       <c r="P254" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q254" s="4" t="n"/>
@@ -20115,7 +20115,7 @@
       </c>
       <c r="P255" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q255" s="4" t="n"/>
@@ -20194,7 +20194,7 @@
       </c>
       <c r="P256" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q256" s="4" t="n"/>
@@ -20273,7 +20273,7 @@
       </c>
       <c r="P257" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q257" s="4" t="n"/>
@@ -20352,7 +20352,7 @@
       </c>
       <c r="P258" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q258" s="4" t="n"/>
@@ -20431,7 +20431,7 @@
       </c>
       <c r="P259" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q259" s="4" t="n"/>
@@ -20510,7 +20510,7 @@
       </c>
       <c r="P260" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q260" s="4" t="n"/>
@@ -20589,7 +20589,7 @@
       </c>
       <c r="P261" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q261" s="4" t="n"/>
@@ -20666,7 +20666,7 @@
       </c>
       <c r="P262" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q262" s="4" t="n"/>
@@ -20743,7 +20743,7 @@
       </c>
       <c r="P263" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q263" s="4" t="n"/>
@@ -20822,7 +20822,7 @@
       </c>
       <c r="P264" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q264" s="4" t="n"/>
@@ -20901,7 +20901,7 @@
       </c>
       <c r="P265" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q265" s="4" t="n"/>
@@ -20980,7 +20980,7 @@
       </c>
       <c r="P266" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q266" s="4" t="n"/>
@@ -21059,7 +21059,7 @@
       </c>
       <c r="P267" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q267" s="4" t="n"/>
@@ -21138,7 +21138,7 @@
       </c>
       <c r="P268" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q268" s="4" t="n"/>
@@ -21217,7 +21217,7 @@
       </c>
       <c r="P269" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q269" s="4" t="n"/>
@@ -21294,7 +21294,7 @@
       </c>
       <c r="P270" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q270" s="4" t="n"/>
@@ -21379,7 +21379,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
